--- a/MathAn/tdxFSCode.xlsx
+++ b/MathAn/tdxFSCode.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7800"/>
+    <workbookView windowWidth="20925" windowHeight="9780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="1204">
   <si>
     <t>Code</t>
   </si>
@@ -46,7 +46,7 @@
     <t>col2</t>
   </si>
   <si>
-    <t>扣除非经常性损益每股收益</t>
+    <t>扣非每股收益</t>
   </si>
   <si>
     <t>deductEPS</t>
@@ -82,1894 +82,1909 @@
     <t>col6</t>
   </si>
   <si>
-    <t>净资产收益率（每股指标=197）</t>
-  </si>
-  <si>
-    <t>ROE</t>
+    <t>每股净资产收益率</t>
+  </si>
+  <si>
+    <t>ROE 197</t>
   </si>
   <si>
     <t>col7</t>
   </si>
   <si>
-    <t>每股经营现金流量（每股指标=219）</t>
+    <t>每股经营现金流量</t>
+  </si>
+  <si>
+    <t>operatingCashFlowPerShare 219</t>
+  </si>
+  <si>
+    <t>col8</t>
+  </si>
+  <si>
+    <t>货币资金</t>
+  </si>
+  <si>
+    <t>moneyFunds</t>
+  </si>
+  <si>
+    <t>col9</t>
+  </si>
+  <si>
+    <t>交易性金融资产</t>
+  </si>
+  <si>
+    <t>tradingFinancialAssets</t>
+  </si>
+  <si>
+    <t>col10</t>
+  </si>
+  <si>
+    <t>应收票据</t>
+  </si>
+  <si>
+    <t>billsReceivables</t>
+  </si>
+  <si>
+    <t>col11</t>
+  </si>
+  <si>
+    <t>应收账款</t>
+  </si>
+  <si>
+    <t>accountsReceivables</t>
+  </si>
+  <si>
+    <t>col12</t>
+  </si>
+  <si>
+    <t>预付款项</t>
+  </si>
+  <si>
+    <t>prepayments</t>
+  </si>
+  <si>
+    <t>col13</t>
+  </si>
+  <si>
+    <t>其他应收款</t>
+  </si>
+  <si>
+    <t>otherReceivables</t>
+  </si>
+  <si>
+    <t>col14</t>
+  </si>
+  <si>
+    <t>应收关联公司款</t>
+  </si>
+  <si>
+    <t>interCompanyReceivables</t>
+  </si>
+  <si>
+    <t>col15</t>
+  </si>
+  <si>
+    <t>应收利息</t>
+  </si>
+  <si>
+    <t>interestReceivables</t>
+  </si>
+  <si>
+    <t>col16</t>
+  </si>
+  <si>
+    <t>应收股利</t>
+  </si>
+  <si>
+    <t>dividendsReceivables</t>
+  </si>
+  <si>
+    <t>col17</t>
+  </si>
+  <si>
+    <t>存货</t>
+  </si>
+  <si>
+    <t>inventory</t>
+  </si>
+  <si>
+    <t>col18</t>
+  </si>
+  <si>
+    <t>其中：消耗性生物资产</t>
+  </si>
+  <si>
+    <t>expendableBiologicalAssets</t>
+  </si>
+  <si>
+    <t>col19</t>
+  </si>
+  <si>
+    <t>一年内到期的非流动资产</t>
+  </si>
+  <si>
+    <t>noncurrentAssetsDueWithinOneYear</t>
+  </si>
+  <si>
+    <t>col20</t>
+  </si>
+  <si>
+    <t>其他流动资产</t>
+  </si>
+  <si>
+    <t>otherLiquidAssets</t>
+  </si>
+  <si>
+    <t>col21</t>
+  </si>
+  <si>
+    <t>流动资产合计</t>
+  </si>
+  <si>
+    <t>totalLiquidAssets</t>
+  </si>
+  <si>
+    <t>col22</t>
+  </si>
+  <si>
+    <t>可供出售金融资产</t>
+  </si>
+  <si>
+    <t>availableForSaleSecurities</t>
+  </si>
+  <si>
+    <t>col23</t>
+  </si>
+  <si>
+    <t>持有至到期投资</t>
+  </si>
+  <si>
+    <t>heldToMaturityInvestments</t>
+  </si>
+  <si>
+    <t>col24</t>
+  </si>
+  <si>
+    <t>长期应收款</t>
+  </si>
+  <si>
+    <t>longTermReceivables</t>
+  </si>
+  <si>
+    <t>col25</t>
+  </si>
+  <si>
+    <t>长期股权投资</t>
+  </si>
+  <si>
+    <t>longTermEquityInvestment</t>
+  </si>
+  <si>
+    <t>col26</t>
+  </si>
+  <si>
+    <t>投资性房地产</t>
+  </si>
+  <si>
+    <t>investmentRealEstate</t>
+  </si>
+  <si>
+    <t>col27</t>
+  </si>
+  <si>
+    <t>固定资产</t>
+  </si>
+  <si>
+    <t>fixedAssets</t>
+  </si>
+  <si>
+    <t>col28</t>
+  </si>
+  <si>
+    <t>在建工程</t>
+  </si>
+  <si>
+    <t>constructionInProgress</t>
+  </si>
+  <si>
+    <t>col29</t>
+  </si>
+  <si>
+    <t>工程物资</t>
+  </si>
+  <si>
+    <t>engineerMaterial</t>
+  </si>
+  <si>
+    <t>col30</t>
+  </si>
+  <si>
+    <t>固定资产清理</t>
+  </si>
+  <si>
+    <t>fixedAssetsCleanUp</t>
+  </si>
+  <si>
+    <t>col31</t>
+  </si>
+  <si>
+    <t>生产性生物资产</t>
+  </si>
+  <si>
+    <t>productiveBiologicalAssets</t>
+  </si>
+  <si>
+    <t>col32</t>
+  </si>
+  <si>
+    <t>油气资产</t>
+  </si>
+  <si>
+    <t>oilAndGasAssets</t>
+  </si>
+  <si>
+    <t>col33</t>
+  </si>
+  <si>
+    <t>无形资产</t>
+  </si>
+  <si>
+    <t>intangibleAssets</t>
+  </si>
+  <si>
+    <t>col34</t>
+  </si>
+  <si>
+    <t>开发支出</t>
+  </si>
+  <si>
+    <t>developmentExpenditure</t>
+  </si>
+  <si>
+    <t>col35</t>
+  </si>
+  <si>
+    <t>商誉</t>
+  </si>
+  <si>
+    <t>goodwill</t>
+  </si>
+  <si>
+    <t>col36</t>
+  </si>
+  <si>
+    <t>长期待摊费用</t>
+  </si>
+  <si>
+    <t>longTermDeferredExpenses</t>
+  </si>
+  <si>
+    <t>col37</t>
+  </si>
+  <si>
+    <t>递延所得税资产</t>
+  </si>
+  <si>
+    <t>deferredIncomeTaxAssets</t>
+  </si>
+  <si>
+    <t>col38</t>
+  </si>
+  <si>
+    <t>其他非流动资产</t>
+  </si>
+  <si>
+    <t>otherNonCurrentAssets</t>
+  </si>
+  <si>
+    <t>col39</t>
+  </si>
+  <si>
+    <t>非流动资产合计</t>
+  </si>
+  <si>
+    <t>totalNonCurrentAssets</t>
+  </si>
+  <si>
+    <t>col40</t>
+  </si>
+  <si>
+    <t>资产总计</t>
+  </si>
+  <si>
+    <t>totalAssets</t>
+  </si>
+  <si>
+    <t>col41</t>
+  </si>
+  <si>
+    <t>短期借款</t>
+  </si>
+  <si>
+    <t>shortTermLoan</t>
+  </si>
+  <si>
+    <t>col42</t>
+  </si>
+  <si>
+    <t>交易性金融负债</t>
+  </si>
+  <si>
+    <t>tradingFinancialLiabilities</t>
+  </si>
+  <si>
+    <t>col43</t>
+  </si>
+  <si>
+    <t>应付票据</t>
+  </si>
+  <si>
+    <t>billsPayable</t>
+  </si>
+  <si>
+    <t>col44</t>
+  </si>
+  <si>
+    <t>应付账款</t>
+  </si>
+  <si>
+    <t>accountsPayable</t>
+  </si>
+  <si>
+    <t>col45</t>
+  </si>
+  <si>
+    <t>预收款项</t>
+  </si>
+  <si>
+    <t>advancedReceivable</t>
+  </si>
+  <si>
+    <t>col46</t>
+  </si>
+  <si>
+    <t>应付职工薪酬</t>
+  </si>
+  <si>
+    <t>employeesPayable</t>
+  </si>
+  <si>
+    <t>col47</t>
+  </si>
+  <si>
+    <t>应交税费</t>
+  </si>
+  <si>
+    <t>taxPayable</t>
+  </si>
+  <si>
+    <t>col48</t>
+  </si>
+  <si>
+    <t>应付利息</t>
+  </si>
+  <si>
+    <t>interestPayable</t>
+  </si>
+  <si>
+    <t>col49</t>
+  </si>
+  <si>
+    <t>应付股利</t>
+  </si>
+  <si>
+    <t>dividendPayable</t>
+  </si>
+  <si>
+    <t>col50</t>
+  </si>
+  <si>
+    <t>其他应付款</t>
+  </si>
+  <si>
+    <t>otherPayable</t>
+  </si>
+  <si>
+    <t>col51</t>
+  </si>
+  <si>
+    <t>应付关联公司款</t>
+  </si>
+  <si>
+    <t>interCompanyPayable</t>
+  </si>
+  <si>
+    <t>col52</t>
+  </si>
+  <si>
+    <t>一年内到期的非流动负债</t>
+  </si>
+  <si>
+    <t>noncurrentLiabilitiesDueWithinOneYear</t>
+  </si>
+  <si>
+    <t>col53</t>
+  </si>
+  <si>
+    <t>其他流动负债</t>
+  </si>
+  <si>
+    <t>otherCurrentLiabilities</t>
+  </si>
+  <si>
+    <t>col54</t>
+  </si>
+  <si>
+    <t>流动负债合计</t>
+  </si>
+  <si>
+    <t>totalCurrentLiabilities</t>
+  </si>
+  <si>
+    <t>col55</t>
+  </si>
+  <si>
+    <t>长期借款</t>
+  </si>
+  <si>
+    <t>longTermLoans</t>
+  </si>
+  <si>
+    <t>col56</t>
+  </si>
+  <si>
+    <t>应付债券</t>
+  </si>
+  <si>
+    <t>bondsPayable</t>
+  </si>
+  <si>
+    <t>col57</t>
+  </si>
+  <si>
+    <t>长期应付款</t>
+  </si>
+  <si>
+    <t>longTermPayable</t>
+  </si>
+  <si>
+    <t>col58</t>
+  </si>
+  <si>
+    <t>专项应付款</t>
+  </si>
+  <si>
+    <t>specialPayable</t>
+  </si>
+  <si>
+    <t>col59</t>
+  </si>
+  <si>
+    <t>预计负债</t>
+  </si>
+  <si>
+    <t>estimatedLiabilities</t>
+  </si>
+  <si>
+    <t>col60</t>
+  </si>
+  <si>
+    <t>递延所得税负债</t>
+  </si>
+  <si>
+    <t>defferredIncomeTaxLiabilities</t>
+  </si>
+  <si>
+    <t>col61</t>
+  </si>
+  <si>
+    <t>其他非流动负债</t>
+  </si>
+  <si>
+    <t>otherNonCurrentLiabilities</t>
+  </si>
+  <si>
+    <t>col62</t>
+  </si>
+  <si>
+    <t>非流动负债合计</t>
+  </si>
+  <si>
+    <t>totalNonCurrentLiabilities</t>
+  </si>
+  <si>
+    <t>col63</t>
+  </si>
+  <si>
+    <t>负债合计</t>
+  </si>
+  <si>
+    <t>totalLiabilities</t>
+  </si>
+  <si>
+    <t>col64</t>
+  </si>
+  <si>
+    <t>实收资本或股本</t>
+  </si>
+  <si>
+    <t>totalShare</t>
+  </si>
+  <si>
+    <t>col65</t>
+  </si>
+  <si>
+    <t>资本公积</t>
+  </si>
+  <si>
+    <t>capitalReserve</t>
+  </si>
+  <si>
+    <t>col66</t>
+  </si>
+  <si>
+    <t>盈余公积</t>
+  </si>
+  <si>
+    <t>surplusReserve</t>
+  </si>
+  <si>
+    <t>col67</t>
+  </si>
+  <si>
+    <t>减：库存股</t>
+  </si>
+  <si>
+    <t>treasuryStock</t>
+  </si>
+  <si>
+    <t>col68</t>
+  </si>
+  <si>
+    <t>未分配利润</t>
+  </si>
+  <si>
+    <t>undistributedProfits</t>
+  </si>
+  <si>
+    <t>col69</t>
+  </si>
+  <si>
+    <t>少数股东权益</t>
+  </si>
+  <si>
+    <t>minorityEquity</t>
+  </si>
+  <si>
+    <t>col70</t>
+  </si>
+  <si>
+    <t>外币报表折算价差</t>
+  </si>
+  <si>
+    <t>foreignCurrencyReportTranslationSpread</t>
+  </si>
+  <si>
+    <t>col71</t>
+  </si>
+  <si>
+    <t>非正常经营项目收益调整</t>
+  </si>
+  <si>
+    <t>abnormalBusinessProjectEarningsAdjustment</t>
+  </si>
+  <si>
+    <t>col72</t>
+  </si>
+  <si>
+    <t>所有者权益（或股东权益）合计</t>
+  </si>
+  <si>
+    <t>totalOwnersEquity</t>
+  </si>
+  <si>
+    <t>col73</t>
+  </si>
+  <si>
+    <t>负债和所有者（或股东权益）合计</t>
+  </si>
+  <si>
+    <t>totalLiabilitiesAndOwnersEquity</t>
+  </si>
+  <si>
+    <t>col74</t>
+  </si>
+  <si>
+    <t>其中：营业收入</t>
+  </si>
+  <si>
+    <t>operatingRevenue</t>
+  </si>
+  <si>
+    <t>col75</t>
+  </si>
+  <si>
+    <t>其中：营业成本</t>
+  </si>
+  <si>
+    <t>operatingCosts</t>
+  </si>
+  <si>
+    <t>col76</t>
+  </si>
+  <si>
+    <t>营业税金及附加</t>
+  </si>
+  <si>
+    <t>taxAndSurcharges</t>
+  </si>
+  <si>
+    <t>col77</t>
+  </si>
+  <si>
+    <t>销售费用</t>
+  </si>
+  <si>
+    <t>salesCosts</t>
+  </si>
+  <si>
+    <t>col78</t>
+  </si>
+  <si>
+    <t>管理费用</t>
+  </si>
+  <si>
+    <t>managementCosts</t>
+  </si>
+  <si>
+    <t>col79</t>
+  </si>
+  <si>
+    <t>堪探费用</t>
+  </si>
+  <si>
+    <t>explorationCosts</t>
+  </si>
+  <si>
+    <t>col80</t>
+  </si>
+  <si>
+    <t>财务费用（利润表）</t>
+  </si>
+  <si>
+    <t>financialCosts</t>
+  </si>
+  <si>
+    <t>col81</t>
+  </si>
+  <si>
+    <t>资产减值损失</t>
+  </si>
+  <si>
+    <t>assestsDevaluation</t>
+  </si>
+  <si>
+    <t>col82</t>
+  </si>
+  <si>
+    <t>加：公允价值变动净收益</t>
+  </si>
+  <si>
+    <t>profitAndLossFromFairValueChanges</t>
+  </si>
+  <si>
+    <t>col83</t>
+  </si>
+  <si>
+    <t>投资收益</t>
+  </si>
+  <si>
+    <t>investmentIncome</t>
+  </si>
+  <si>
+    <t>col84</t>
+  </si>
+  <si>
+    <t>其中：对联营企业和合营企业的投资收益</t>
+  </si>
+  <si>
+    <t>investmentIncomeFromAffiliatedBusinessAndCooperativeEnterprise</t>
+  </si>
+  <si>
+    <t>col85</t>
+  </si>
+  <si>
+    <t>影响营业利润的其他科目</t>
+  </si>
+  <si>
+    <t>otherSubjectsAffectingOperatingProfit</t>
+  </si>
+  <si>
+    <t>col86</t>
+  </si>
+  <si>
+    <t>营业利润</t>
+  </si>
+  <si>
+    <t>operatingProfit</t>
+  </si>
+  <si>
+    <t>col87</t>
+  </si>
+  <si>
+    <t>加：补贴收入</t>
+  </si>
+  <si>
+    <t>subsidyIncome</t>
+  </si>
+  <si>
+    <t>col88</t>
+  </si>
+  <si>
+    <t>营业外收入</t>
+  </si>
+  <si>
+    <t>nonOperatingIncome</t>
+  </si>
+  <si>
+    <t>col89</t>
+  </si>
+  <si>
+    <t>减：营业外支出</t>
+  </si>
+  <si>
+    <t>nonOperatingExpenses</t>
+  </si>
+  <si>
+    <t>col90</t>
+  </si>
+  <si>
+    <t>其中：非流动资产处置净损失</t>
+  </si>
+  <si>
+    <t>netLossFromDisposalOfNonCurrentAssets</t>
+  </si>
+  <si>
+    <t>col91</t>
+  </si>
+  <si>
+    <t>加：影响利润总额的其他科目</t>
+  </si>
+  <si>
+    <t>otherSubjectsAffectTotalProfit</t>
+  </si>
+  <si>
+    <t>col92</t>
+  </si>
+  <si>
+    <t>利润总额</t>
+  </si>
+  <si>
+    <t>totalProfit</t>
+  </si>
+  <si>
+    <t>col93</t>
+  </si>
+  <si>
+    <t>减：所得税</t>
+  </si>
+  <si>
+    <t>incomeTax</t>
+  </si>
+  <si>
+    <t>col94</t>
+  </si>
+  <si>
+    <t>加：影响净利润的其他科目</t>
+  </si>
+  <si>
+    <t>otherSubjectsAffectNetProfit</t>
+  </si>
+  <si>
+    <t>col95</t>
+  </si>
+  <si>
+    <t>净利润（利润表）</t>
+  </si>
+  <si>
+    <t>netProfit 134</t>
+  </si>
+  <si>
+    <t>col96</t>
+  </si>
+  <si>
+    <t>归属母公司所有者净利润</t>
+  </si>
+  <si>
+    <t>netProfitsBelongToParentCompanyOwner</t>
+  </si>
+  <si>
+    <t>col97</t>
+  </si>
+  <si>
+    <t>少数股东损益</t>
+  </si>
+  <si>
+    <t>minorityProfitAndLoss</t>
+  </si>
+  <si>
+    <t>col98</t>
+  </si>
+  <si>
+    <t>销售商品、提供劳务收到的现金</t>
+  </si>
+  <si>
+    <t>cashFromGoodsSalesorOrRenderingOfServices</t>
+  </si>
+  <si>
+    <t>col99</t>
+  </si>
+  <si>
+    <t>收到的税费返还</t>
+  </si>
+  <si>
+    <t>refundOfTaxAndFeeReceived</t>
+  </si>
+  <si>
+    <t>col100</t>
+  </si>
+  <si>
+    <t>收到其他与经营活动有关的现金</t>
+  </si>
+  <si>
+    <t>otherCashRelatedBusinessActivitiesReceived</t>
+  </si>
+  <si>
+    <t>col101</t>
+  </si>
+  <si>
+    <t>经营活动现金流入小计</t>
+  </si>
+  <si>
+    <t>cashInflowsFromOperatingActivities</t>
+  </si>
+  <si>
+    <t>col102</t>
+  </si>
+  <si>
+    <t>购买商品、接受劳务支付的现金</t>
+  </si>
+  <si>
+    <t>buyingGoodsReceivingCashPaidForLabor</t>
+  </si>
+  <si>
+    <t>col103</t>
+  </si>
+  <si>
+    <t>支付给职工以及为职工支付的现金</t>
+  </si>
+  <si>
+    <t>paymentToEmployeesAndCashPaidForEmployees</t>
+  </si>
+  <si>
+    <t>col104</t>
+  </si>
+  <si>
+    <t>支付的各项税费</t>
+  </si>
+  <si>
+    <t>paymentsOfVariousTaxes</t>
+  </si>
+  <si>
+    <t>col105</t>
+  </si>
+  <si>
+    <t>支付其他与经营活动有关的现金</t>
+  </si>
+  <si>
+    <t>paymentOfOtherCashRelatedToBusinessActivities</t>
+  </si>
+  <si>
+    <t>col106</t>
+  </si>
+  <si>
+    <t>经营活动现金流出小计</t>
+  </si>
+  <si>
+    <t>cashOutflowsFromOperatingActivities</t>
+  </si>
+  <si>
+    <t>col107</t>
+  </si>
+  <si>
+    <t>经营活动产生的现金流量净额（现金流量表）</t>
+  </si>
+  <si>
+    <t>netCashFlowsFromOperatingActivities 150</t>
+  </si>
+  <si>
+    <t>col108</t>
+  </si>
+  <si>
+    <t>收回投资收到的现金</t>
+  </si>
+  <si>
+    <t>cashReceivedFromInvestmentReceived</t>
+  </si>
+  <si>
+    <t>col109</t>
+  </si>
+  <si>
+    <t>取得投资收益收到的现金</t>
+  </si>
+  <si>
+    <t>cashReceivedFromInvestmentIncome</t>
+  </si>
+  <si>
+    <t>col110</t>
+  </si>
+  <si>
+    <t>处置固定资产、无形资产和其他长期资产收回的现金净额</t>
+  </si>
+  <si>
+    <t>disposalOfNetCashForRecoveryOfFixedAssetsIntangibleAssetsAndOtherLongTermAssets</t>
+  </si>
+  <si>
+    <t>col111</t>
+  </si>
+  <si>
+    <t>处置子公司及其他营业单位收到的现金净额</t>
+  </si>
+  <si>
+    <t>disposalOfNetCashReceivedFromSubsidiariesAndOtherBusinessUnits</t>
+  </si>
+  <si>
+    <t>col112</t>
+  </si>
+  <si>
+    <t>收到其他与投资活动有关的现金</t>
+  </si>
+  <si>
+    <t>otherCashReceivedRelatingToInvestingActivities</t>
+  </si>
+  <si>
+    <t>col113</t>
+  </si>
+  <si>
+    <t>投资活动现金流入小计</t>
+  </si>
+  <si>
+    <t>cashinFlowsFromInvestmentActivities</t>
+  </si>
+  <si>
+    <t>col114</t>
+  </si>
+  <si>
+    <t>购建固定资产、无形资产和其他长期资产支付的现金</t>
+  </si>
+  <si>
+    <t>cashForThePurchaseConstructionPaymentOfFixedAssetsIntangibleAssetsAndOtherLongTermAssets</t>
+  </si>
+  <si>
+    <t>col115</t>
+  </si>
+  <si>
+    <t>投资支付的现金</t>
+  </si>
+  <si>
+    <t>cashInvestment</t>
+  </si>
+  <si>
+    <t>col116</t>
+  </si>
+  <si>
+    <t>取得子公司及其他营业单位支付的现金净额</t>
+  </si>
+  <si>
+    <t>acquisitionOfNetCashPaidBySubsidiariesAndOtherBusinessUnits</t>
+  </si>
+  <si>
+    <t>col117</t>
+  </si>
+  <si>
+    <t>支付其他与投资活动有关的现金</t>
+  </si>
+  <si>
+    <t>otherCashPaidRelatingToInvestingActivities</t>
+  </si>
+  <si>
+    <t>col118</t>
+  </si>
+  <si>
+    <t>投资活动现金流出小计</t>
+  </si>
+  <si>
+    <t>cashOutflowsFromInvestmentActivities</t>
+  </si>
+  <si>
+    <t>col119</t>
+  </si>
+  <si>
+    <t>投资活动产生的现金流量净额</t>
+  </si>
+  <si>
+    <t>netCashFlowsFromInvestingActivities</t>
+  </si>
+  <si>
+    <t>col120</t>
+  </si>
+  <si>
+    <t>吸收投资收到的现金</t>
+  </si>
+  <si>
+    <t>cashReceivedFromInvestors</t>
+  </si>
+  <si>
+    <t>col121</t>
+  </si>
+  <si>
+    <t>取得借款收到的现金</t>
+  </si>
+  <si>
+    <t>cashFromBorrowings</t>
+  </si>
+  <si>
+    <t>col122</t>
+  </si>
+  <si>
+    <t>收到其他与筹资活动有关的现金</t>
+  </si>
+  <si>
+    <t>otherCashReceivedRelatingToFinancingActivities</t>
+  </si>
+  <si>
+    <t>col123</t>
+  </si>
+  <si>
+    <t>筹资活动现金流入小计</t>
+  </si>
+  <si>
+    <t>cashInflowsFromFinancingActivities</t>
+  </si>
+  <si>
+    <t>col124</t>
+  </si>
+  <si>
+    <t>偿还债务支付的现金</t>
+  </si>
+  <si>
+    <t>cashPaymentsOfAmountBorrowed</t>
+  </si>
+  <si>
+    <t>col125</t>
+  </si>
+  <si>
+    <t>分配股利、利润或偿付利息支付的现金</t>
+  </si>
+  <si>
+    <t>cashPaymentsForDistrbutionOfDividendsOrProfits</t>
+  </si>
+  <si>
+    <t>col126</t>
+  </si>
+  <si>
+    <t>支付其他与筹资活动有关的现金</t>
+  </si>
+  <si>
+    <t>otherCashPaymentRelatingToFinancingActivities</t>
+  </si>
+  <si>
+    <t>col127</t>
+  </si>
+  <si>
+    <t>筹资活动现金流出小计</t>
+  </si>
+  <si>
+    <t>cashOutflowsFromFinancingActivities</t>
+  </si>
+  <si>
+    <t>col128</t>
+  </si>
+  <si>
+    <t>筹资活动产生的现金流量净额</t>
+  </si>
+  <si>
+    <t>netCashFlowsFromFinancingActivities</t>
+  </si>
+  <si>
+    <t>col129</t>
+  </si>
+  <si>
+    <t>汇率变动对现金的影响</t>
+  </si>
+  <si>
+    <t>effectOfForeignExchangRateChangesOnCash</t>
+  </si>
+  <si>
+    <t>col130</t>
+  </si>
+  <si>
+    <t>其他原因对现金的影响（汇率变动）</t>
+  </si>
+  <si>
+    <t>effectOfOtherReasonOnCash</t>
+  </si>
+  <si>
+    <t>col131</t>
+  </si>
+  <si>
+    <t>现金及现金等价物净增加额</t>
+  </si>
+  <si>
+    <t>netIncreaseInCashAndCashEquivalents 158</t>
+  </si>
+  <si>
+    <t>col132</t>
+  </si>
+  <si>
+    <t>期初现金及现金等价物余额</t>
+  </si>
+  <si>
+    <t>initialCashAndCashEquivalentsBalance</t>
+  </si>
+  <si>
+    <t>col133</t>
+  </si>
+  <si>
+    <t>期末现金及现金等价物余额</t>
+  </si>
+  <si>
+    <t>theFinalCashAndCashEquivalentsBalance</t>
+  </si>
+  <si>
+    <t>col134</t>
+  </si>
+  <si>
+    <t>净利润（现金流量附表）</t>
+  </si>
+  <si>
+    <t>netProfitFromOperatingActivities 95</t>
+  </si>
+  <si>
+    <t>col135</t>
+  </si>
+  <si>
+    <t>资产减值准备</t>
+  </si>
+  <si>
+    <t>provisionForAssetsLosses</t>
+  </si>
+  <si>
+    <t>col136</t>
+  </si>
+  <si>
+    <t>固定资产折旧、油气资产折耗、生产性生物资产折旧</t>
+  </si>
+  <si>
+    <t>depreciationForFixedAssets</t>
+  </si>
+  <si>
+    <t>col137</t>
+  </si>
+  <si>
+    <t>无形资产摊销</t>
+  </si>
+  <si>
+    <t>amortizationOfIntangibleAssets</t>
+  </si>
+  <si>
+    <t>col138</t>
+  </si>
+  <si>
+    <t>长期待摊费用摊销</t>
+  </si>
+  <si>
+    <t>amortizationOfLong-termDeferredExpenses</t>
+  </si>
+  <si>
+    <t>col139</t>
+  </si>
+  <si>
+    <t>处置固定资产、无形资产和其他长期资产的损失</t>
+  </si>
+  <si>
+    <t>lossOfDisposingFixedAssetsIntangibleAssetsAndOtherLong-termAssets</t>
+  </si>
+  <si>
+    <t>col140</t>
+  </si>
+  <si>
+    <t>固定资产报废损失</t>
+  </si>
+  <si>
+    <t>scrapLossOfFixedAssets</t>
+  </si>
+  <si>
+    <t>col141</t>
+  </si>
+  <si>
+    <t>公允价值变动损失</t>
+  </si>
+  <si>
+    <t>lossFromFairValueChange</t>
+  </si>
+  <si>
+    <t>col142</t>
+  </si>
+  <si>
+    <t>财务费用（现金流量表）</t>
+  </si>
+  <si>
+    <t>financialExpenses</t>
+  </si>
+  <si>
+    <t>col143</t>
+  </si>
+  <si>
+    <t>投资损失</t>
+  </si>
+  <si>
+    <t>investmentLosses</t>
+  </si>
+  <si>
+    <t>col144</t>
+  </si>
+  <si>
+    <t>递延所得税资产减少</t>
+  </si>
+  <si>
+    <t>decreaseOfDeferredTaxAssets</t>
+  </si>
+  <si>
+    <t>col145</t>
+  </si>
+  <si>
+    <t>递延所得税负债增加</t>
+  </si>
+  <si>
+    <t>increaseOfDeferredTaxLiabilities</t>
+  </si>
+  <si>
+    <t>col146</t>
+  </si>
+  <si>
+    <t>存货的减少</t>
+  </si>
+  <si>
+    <t>decreaseOfInventory</t>
+  </si>
+  <si>
+    <t>col147</t>
+  </si>
+  <si>
+    <t>经营性应收项目的减少</t>
+  </si>
+  <si>
+    <t>decreaseOfOperationReceivables</t>
+  </si>
+  <si>
+    <t>col148</t>
+  </si>
+  <si>
+    <t>经营性应付项目的增加</t>
+  </si>
+  <si>
+    <t>increaseOfOperationPayables</t>
+  </si>
+  <si>
+    <t>col149</t>
+  </si>
+  <si>
+    <t>其他（现金流量补充表）</t>
+  </si>
+  <si>
+    <t>col150</t>
+  </si>
+  <si>
+    <t>经营活动产生的现金流量净额（现金流量附表）</t>
+  </si>
+  <si>
+    <t>netCashFromOperatingActivities2 107</t>
+  </si>
+  <si>
+    <t>col151</t>
+  </si>
+  <si>
+    <t>债务转为资本</t>
+  </si>
+  <si>
+    <t>debtConvertedToCSapital</t>
+  </si>
+  <si>
+    <t>col152</t>
+  </si>
+  <si>
+    <t>一年内到期的可转换公司债券</t>
+  </si>
+  <si>
+    <t>convertibleBondMaturityWithinOneYear</t>
+  </si>
+  <si>
+    <t>col153</t>
+  </si>
+  <si>
+    <t>融资租入固定资产</t>
+  </si>
+  <si>
+    <t>leaseholdImprovements</t>
+  </si>
+  <si>
+    <t>col154</t>
+  </si>
+  <si>
+    <t>现金的期末余额</t>
+  </si>
+  <si>
+    <t>cashEndingBal</t>
+  </si>
+  <si>
+    <t>col155</t>
+  </si>
+  <si>
+    <t>现金的期初余额</t>
+  </si>
+  <si>
+    <t>cashBeginingBal</t>
+  </si>
+  <si>
+    <t>col156</t>
+  </si>
+  <si>
+    <t>现金等价物的期末余额</t>
+  </si>
+  <si>
+    <t>cashEquivalentsEndingBal</t>
+  </si>
+  <si>
+    <t>col157</t>
+  </si>
+  <si>
+    <t>现金等价物的期初余额</t>
+  </si>
+  <si>
+    <t>cashEquivalentsBeginningBal</t>
+  </si>
+  <si>
+    <t>col158</t>
+  </si>
+  <si>
+    <t>现金及现金等价物净增加额（补充项）</t>
+  </si>
+  <si>
+    <t>netIncreaseOfCashAndCashEquivalents 131</t>
+  </si>
+  <si>
+    <t>col159</t>
+  </si>
+  <si>
+    <t>流动比率</t>
+  </si>
+  <si>
+    <t>currentRatio  # 流动资产/流动负债</t>
+  </si>
+  <si>
+    <t>col160</t>
+  </si>
+  <si>
+    <t>速动比率</t>
+  </si>
+  <si>
+    <t>acidTestRatio  # (流动资产-存货）/流动负债</t>
+  </si>
+  <si>
+    <t>col161</t>
+  </si>
+  <si>
+    <t>现金比率</t>
+  </si>
+  <si>
+    <t>cashRatio  # (货币资金+有价证券)÷流动负债</t>
+  </si>
+  <si>
+    <t>col162</t>
+  </si>
+  <si>
+    <t>利息保障倍数</t>
+  </si>
+  <si>
+    <t>interestCoverageRatio  # (利润总额+财务费用（仅指利息费用部份）)/利息费用</t>
+  </si>
+  <si>
+    <t>col163</t>
+  </si>
+  <si>
+    <t>非流动负债比率</t>
+  </si>
+  <si>
+    <t>noncurrentLiabilitiesRatio</t>
+  </si>
+  <si>
+    <t>col164</t>
+  </si>
+  <si>
+    <t>流动负债比率</t>
+  </si>
+  <si>
+    <t>currentLiabilitiesRatio</t>
+  </si>
+  <si>
+    <t>col165</t>
+  </si>
+  <si>
+    <t>现金到期债务比率</t>
+  </si>
+  <si>
+    <t>cashDebtRatio  # 企业经营现金净流入/(本期到期长期负债+本期应付票据)</t>
+  </si>
+  <si>
+    <t>col166</t>
+  </si>
+  <si>
+    <t>有形资产净值债务率</t>
+  </si>
+  <si>
+    <t>debtToTangibleAssetsRatio</t>
+  </si>
+  <si>
+    <t>col167</t>
+  </si>
+  <si>
+    <t>权益乘数</t>
+  </si>
+  <si>
+    <t>equityMultiplier  # 资产总额/股东权益总额</t>
+  </si>
+  <si>
+    <t>col168</t>
+  </si>
+  <si>
+    <t>股东的权益/负债合计</t>
+  </si>
+  <si>
+    <t>equityDebtRatio  # 权益负债率</t>
+  </si>
+  <si>
+    <t>col169</t>
+  </si>
+  <si>
+    <t>有形资产/负债合计</t>
+  </si>
+  <si>
+    <t>tangibleAssetDebtRatio   # 有形资产负债率</t>
+  </si>
+  <si>
+    <t>col170</t>
+  </si>
+  <si>
+    <t>经营活动产生的现金流量净额/负债合计</t>
+  </si>
+  <si>
+    <t>netCashFlowsFromOperatingActivitiesDebtRatio</t>
+  </si>
+  <si>
+    <t>col171</t>
+  </si>
+  <si>
+    <t>税息折旧及摊销前利润/负债合计</t>
+  </si>
+  <si>
+    <t>EBITDA/Liabilities</t>
+  </si>
+  <si>
+    <t>col172</t>
+  </si>
+  <si>
+    <t>应收帐款周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfReceivable</t>
+  </si>
+  <si>
+    <t>col173</t>
+  </si>
+  <si>
+    <t>存货周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfInventory</t>
+  </si>
+  <si>
+    <t>col174</t>
+  </si>
+  <si>
+    <t>运营资金周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfOperatingAssets</t>
+  </si>
+  <si>
+    <t>col175</t>
+  </si>
+  <si>
+    <t>总资产周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfTotalAssets</t>
+  </si>
+  <si>
+    <t>col176</t>
+  </si>
+  <si>
+    <t>固定资产周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfFixedAssets  # 企业销售收入与固定资产净值的比率</t>
+  </si>
+  <si>
+    <t>col177</t>
+  </si>
+  <si>
+    <t>应收帐款周转天数</t>
+  </si>
+  <si>
+    <t>daysSalesOutstanding  # 企业从取得应收账款的权利到收回款项、转换为现金所需要的时间</t>
+  </si>
+  <si>
+    <t>col178</t>
+  </si>
+  <si>
+    <t>存货周转天数</t>
+  </si>
+  <si>
+    <t>daysSalesOfInventory  # 企业从取得存货开始至消耗、销售为止所经历的天数</t>
+  </si>
+  <si>
+    <t>col179</t>
+  </si>
+  <si>
+    <t>流动资产周转率</t>
+  </si>
+  <si>
+    <t>turnoverRatioOfCurrentAssets  # 流动资产周转率(次)=主营业务收入/平均流动资产总额</t>
+  </si>
+  <si>
+    <t>col180</t>
+  </si>
+  <si>
+    <t>流动资产周转天数</t>
+  </si>
+  <si>
+    <t>daysSalesofCurrentAssets</t>
+  </si>
+  <si>
+    <t>col181</t>
+  </si>
+  <si>
+    <t>总资产周转天数</t>
+  </si>
+  <si>
+    <t>daysSalesofTotalAssets</t>
+  </si>
+  <si>
+    <t>col182</t>
+  </si>
+  <si>
+    <t>股东权益周转率</t>
+  </si>
+  <si>
+    <t>equityTurnover  # 销售收入/平均股东权益</t>
+  </si>
+  <si>
+    <t>col183</t>
+  </si>
+  <si>
+    <t>营业总收入同比增长率</t>
+  </si>
+  <si>
+    <t>operatingIncomeGrowth</t>
+  </si>
+  <si>
+    <t>col184</t>
+  </si>
+  <si>
+    <t>净利润同比增长率</t>
+  </si>
+  <si>
+    <t>netProfitGrowthRate  # NPGR  利润总额－所得税</t>
+  </si>
+  <si>
+    <t>col185</t>
+  </si>
+  <si>
+    <t>净资产增长率</t>
+  </si>
+  <si>
+    <t>netAssetsGrowthRate</t>
+  </si>
+  <si>
+    <t>col186</t>
+  </si>
+  <si>
+    <t>固定资产增长率</t>
+  </si>
+  <si>
+    <t>fixedAssetsGrowthRate</t>
+  </si>
+  <si>
+    <t>col187</t>
+  </si>
+  <si>
+    <t>总资产增长率</t>
+  </si>
+  <si>
+    <t>totalAssetsGrowthRate</t>
+  </si>
+  <si>
+    <t>col188</t>
+  </si>
+  <si>
+    <t>投资收益增长率</t>
+  </si>
+  <si>
+    <t>investmentIncomeGrowthRate</t>
+  </si>
+  <si>
+    <t>col189</t>
+  </si>
+  <si>
+    <t>营业利润增长率</t>
+  </si>
+  <si>
+    <t>operatingProfitGrowthRate</t>
+  </si>
+  <si>
+    <t>col191</t>
+  </si>
+  <si>
+    <t>扣非净利润同比增长率</t>
+  </si>
+  <si>
+    <t>col193</t>
+  </si>
+  <si>
+    <t>成本费用利润率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnCost</t>
+  </si>
+  <si>
+    <t>col194</t>
+  </si>
+  <si>
+    <t>营业利润率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnOperatingProfit</t>
+  </si>
+  <si>
+    <t>col195</t>
+  </si>
+  <si>
+    <t>营业税金率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnBusinessTax</t>
+  </si>
+  <si>
+    <t>col196</t>
+  </si>
+  <si>
+    <t>营业成本率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnOperatingCost</t>
+  </si>
+  <si>
+    <t>col197</t>
+  </si>
+  <si>
+    <t>净资产收益率（获利能力分析）</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnCommonStockholdersEquity 6</t>
+  </si>
+  <si>
+    <t>col198</t>
+  </si>
+  <si>
+    <t>投资收益率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnInvestmentIncome</t>
+  </si>
+  <si>
+    <t>col199</t>
+  </si>
+  <si>
+    <t>销售净利率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnNetSalesProfit</t>
+  </si>
+  <si>
+    <t>col200</t>
+  </si>
+  <si>
+    <t>总资产报酬率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnTotalAssets</t>
+  </si>
+  <si>
+    <t>col201</t>
+  </si>
+  <si>
+    <t>净利润率</t>
+  </si>
+  <si>
+    <t>netProfitMargin</t>
+  </si>
+  <si>
+    <t>col202</t>
+  </si>
+  <si>
+    <t>销售毛利率</t>
+  </si>
+  <si>
+    <t>rateOfReturnOnGrossProfitFromSales</t>
+  </si>
+  <si>
+    <t>col203</t>
+  </si>
+  <si>
+    <t>三费比重</t>
+  </si>
+  <si>
+    <t>threeFeeProportion</t>
+  </si>
+  <si>
+    <t>col204</t>
+  </si>
+  <si>
+    <t>管理费用率</t>
+  </si>
+  <si>
+    <t>ratioOfChargingExpense</t>
+  </si>
+  <si>
+    <t>col205</t>
+  </si>
+  <si>
+    <t>财务费用率</t>
+  </si>
+  <si>
+    <t>ratioOfFinancialExpense</t>
+  </si>
+  <si>
+    <t>col206</t>
+  </si>
+  <si>
+    <t>扣非净利润</t>
+  </si>
+  <si>
+    <t>netProfitAfterExtraordinaryGainsAndLosses</t>
+  </si>
+  <si>
+    <t>col207</t>
+  </si>
+  <si>
+    <t>息税前利润(EBIT)</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>col208</t>
+  </si>
+  <si>
+    <t>息税折旧摊销前利润(EBITDA)</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>col209</t>
+  </si>
+  <si>
+    <t>EBITDA/营业总收入</t>
+  </si>
+  <si>
+    <t>EBITDA/GrossRevenueRate</t>
+  </si>
+  <si>
+    <t>col210</t>
+  </si>
+  <si>
+    <t>资产负债率</t>
+  </si>
+  <si>
+    <t>assetsLiabilitiesRatio</t>
+  </si>
+  <si>
+    <t>col211</t>
+  </si>
+  <si>
+    <t>流动资产比率</t>
+  </si>
+  <si>
+    <t>currentAssetsRatio  # 期末的流动资产除以所有者权益</t>
+  </si>
+  <si>
+    <t>col212</t>
+  </si>
+  <si>
+    <t>货币资金比率</t>
+  </si>
+  <si>
+    <t>monetaryFundRatio</t>
+  </si>
+  <si>
+    <t>col213</t>
+  </si>
+  <si>
+    <t>存货比率</t>
+  </si>
+  <si>
+    <t>inventoryRatio</t>
+  </si>
+  <si>
+    <t>col214</t>
+  </si>
+  <si>
+    <t>固定资产比率</t>
+  </si>
+  <si>
+    <t>fixedAssetsRatio</t>
+  </si>
+  <si>
+    <t>col215</t>
+  </si>
+  <si>
+    <t>负债结构比</t>
+  </si>
+  <si>
+    <t>liabilitiesStructureRatio</t>
+  </si>
+  <si>
+    <t>col216</t>
+  </si>
+  <si>
+    <t>归属于母公司股东权益/全部投入资本</t>
+  </si>
+  <si>
+    <t>shareholdersOwnershipOfAParentCompany/TotalCapital</t>
+  </si>
+  <si>
+    <t>col217</t>
+  </si>
+  <si>
+    <t>股东的权益/带息债务</t>
+  </si>
+  <si>
+    <t>shareholdersInterest/InterestRateDebtRatio</t>
+  </si>
+  <si>
+    <t>col218</t>
+  </si>
+  <si>
+    <t>有形资产/净债务</t>
+  </si>
+  <si>
+    <t>tangibleAssets/NetDebtRatio</t>
+  </si>
+  <si>
+    <t>col219</t>
+  </si>
+  <si>
+    <t>每股经营现金流（现金流量分析=7）</t>
   </si>
   <si>
     <t>operatingCashFlowPerShare</t>
   </si>
   <si>
-    <t>col8</t>
-  </si>
-  <si>
-    <t>货币资金</t>
-  </si>
-  <si>
-    <t>moneyFunds</t>
-  </si>
-  <si>
-    <t>col9</t>
-  </si>
-  <si>
-    <t>交易性金融资产（元）</t>
-  </si>
-  <si>
-    <t>tradingFinancialAssets</t>
-  </si>
-  <si>
-    <t>col10</t>
-  </si>
-  <si>
-    <t>应收票据</t>
-  </si>
-  <si>
-    <t>billsReceivables</t>
-  </si>
-  <si>
-    <t>col11</t>
-  </si>
-  <si>
-    <t>应收账款</t>
-  </si>
-  <si>
-    <t>accountsReceivables</t>
-  </si>
-  <si>
-    <t>col12</t>
-  </si>
-  <si>
-    <t>预付款项</t>
-  </si>
-  <si>
-    <t>prepayments</t>
-  </si>
-  <si>
-    <t>col13</t>
-  </si>
-  <si>
-    <t>其他应收款</t>
-  </si>
-  <si>
-    <t>otherReceivables</t>
-  </si>
-  <si>
-    <t>col14</t>
-  </si>
-  <si>
-    <t>应收关联公司款</t>
-  </si>
-  <si>
-    <t>interCompanyReceivables</t>
-  </si>
-  <si>
-    <t>col15</t>
-  </si>
-  <si>
-    <t>应收利息</t>
-  </si>
-  <si>
-    <t>interestReceivables</t>
-  </si>
-  <si>
-    <t>col16</t>
-  </si>
-  <si>
-    <t>应收股利</t>
-  </si>
-  <si>
-    <t>dividendsReceivables</t>
-  </si>
-  <si>
-    <t>col17</t>
-  </si>
-  <si>
-    <t>存货</t>
-  </si>
-  <si>
-    <t>inventory</t>
-  </si>
-  <si>
-    <t>col18</t>
-  </si>
-  <si>
-    <t>其中：消耗性生物资产</t>
-  </si>
-  <si>
-    <t>expendableBiologicalAssets</t>
-  </si>
-  <si>
-    <t>col19</t>
-  </si>
-  <si>
-    <t>一年内到期的非流动资产</t>
-  </si>
-  <si>
-    <t>noncurrentAssetsDueWithinOneYear</t>
-  </si>
-  <si>
-    <t>col20</t>
-  </si>
-  <si>
-    <t>其他流动资产</t>
-  </si>
-  <si>
-    <t>otherLiquidAssets</t>
-  </si>
-  <si>
-    <t>col21</t>
-  </si>
-  <si>
-    <t>流动资产合计</t>
-  </si>
-  <si>
-    <t>totalLiquidAssets</t>
-  </si>
-  <si>
-    <t>col22</t>
-  </si>
-  <si>
-    <t>可供出售金融资产</t>
-  </si>
-  <si>
-    <t>availableForSaleSecurities</t>
-  </si>
-  <si>
-    <t>col23</t>
-  </si>
-  <si>
-    <t>持有至到期投资</t>
-  </si>
-  <si>
-    <t>heldToMaturityInvestments</t>
-  </si>
-  <si>
-    <t>col24</t>
-  </si>
-  <si>
-    <t>长期应收款</t>
-  </si>
-  <si>
-    <t>longTermReceivables</t>
-  </si>
-  <si>
-    <t>col25</t>
-  </si>
-  <si>
-    <t>长期股权投资</t>
-  </si>
-  <si>
-    <t>longTermEquityInvestment</t>
-  </si>
-  <si>
-    <t>col26</t>
-  </si>
-  <si>
-    <t>投资性房地产（元）</t>
-  </si>
-  <si>
-    <t>investmentRealEstate</t>
-  </si>
-  <si>
-    <t>col27</t>
-  </si>
-  <si>
-    <t>固定资产（元）</t>
-  </si>
-  <si>
-    <t>fixedAssets</t>
-  </si>
-  <si>
-    <t>col28</t>
-  </si>
-  <si>
-    <t>在建工程</t>
-  </si>
-  <si>
-    <t>constructionInProgress</t>
-  </si>
-  <si>
-    <t>col29</t>
-  </si>
-  <si>
-    <t>工程物资</t>
-  </si>
-  <si>
-    <t>engineerMaterial</t>
-  </si>
-  <si>
-    <t>col30</t>
-  </si>
-  <si>
-    <t>固定资产清理</t>
-  </si>
-  <si>
-    <t>fixedAssetsCleanUp</t>
-  </si>
-  <si>
-    <t>col31</t>
-  </si>
-  <si>
-    <t>生产性生物资产</t>
-  </si>
-  <si>
-    <t>productiveBiologicalAssets</t>
-  </si>
-  <si>
-    <t>col32</t>
-  </si>
-  <si>
-    <t>油气资产</t>
-  </si>
-  <si>
-    <t>oilAndGasAssets</t>
-  </si>
-  <si>
-    <t>col33</t>
-  </si>
-  <si>
-    <t>无形资产</t>
-  </si>
-  <si>
-    <t>intangibleAssets</t>
-  </si>
-  <si>
-    <t>col34</t>
-  </si>
-  <si>
-    <t>开发支出</t>
-  </si>
-  <si>
-    <t>developmentExpenditure</t>
-  </si>
-  <si>
-    <t>col35</t>
-  </si>
-  <si>
-    <t>商誉</t>
-  </si>
-  <si>
-    <t>goodwill</t>
-  </si>
-  <si>
-    <t>col36</t>
-  </si>
-  <si>
-    <t>长期待摊费用</t>
-  </si>
-  <si>
-    <t>longTermDeferredExpenses</t>
-  </si>
-  <si>
-    <t>col37</t>
-  </si>
-  <si>
-    <t>递延所得税资产</t>
-  </si>
-  <si>
-    <t>deferredIncomeTaxAssets</t>
-  </si>
-  <si>
-    <t>col38</t>
-  </si>
-  <si>
-    <t>其他非流动资产</t>
-  </si>
-  <si>
-    <t>otherNonCurrentAssets</t>
-  </si>
-  <si>
-    <t>col39</t>
-  </si>
-  <si>
-    <t>非流动资产合计</t>
-  </si>
-  <si>
-    <t>totalNonCurrentAssets</t>
-  </si>
-  <si>
-    <t>col40</t>
-  </si>
-  <si>
-    <t>资产总计</t>
-  </si>
-  <si>
-    <t>totalAssets</t>
-  </si>
-  <si>
-    <t>col41</t>
-  </si>
-  <si>
-    <t>短期借款</t>
-  </si>
-  <si>
-    <t>shortTermLoan</t>
-  </si>
-  <si>
-    <t>col42</t>
-  </si>
-  <si>
-    <t>交易性金融负债</t>
-  </si>
-  <si>
-    <t>tradingFinancialLiabilities</t>
-  </si>
-  <si>
-    <t>col43</t>
-  </si>
-  <si>
-    <t>应付票据</t>
-  </si>
-  <si>
-    <t>billsPayable</t>
-  </si>
-  <si>
-    <t>col44</t>
-  </si>
-  <si>
-    <t>应付账款</t>
-  </si>
-  <si>
-    <t>accountsPayable</t>
-  </si>
-  <si>
-    <t>col45</t>
-  </si>
-  <si>
-    <t>预收款项</t>
-  </si>
-  <si>
-    <t>advancedReceivable</t>
-  </si>
-  <si>
-    <t>col46</t>
-  </si>
-  <si>
-    <t>应付职工薪酬</t>
-  </si>
-  <si>
-    <t>employeesPayable</t>
-  </si>
-  <si>
-    <t>col47</t>
-  </si>
-  <si>
-    <t>应交税费</t>
-  </si>
-  <si>
-    <t>taxPayable</t>
-  </si>
-  <si>
-    <t>col48</t>
-  </si>
-  <si>
-    <t>应付利息</t>
-  </si>
-  <si>
-    <t>interestPayable</t>
-  </si>
-  <si>
-    <t>col49</t>
-  </si>
-  <si>
-    <t>应付股利</t>
-  </si>
-  <si>
-    <t>dividendPayable</t>
-  </si>
-  <si>
-    <t>col50</t>
-  </si>
-  <si>
-    <t>其他应付款</t>
-  </si>
-  <si>
-    <t>otherPayable</t>
-  </si>
-  <si>
-    <t>col51</t>
-  </si>
-  <si>
-    <t>应付关联公司款</t>
-  </si>
-  <si>
-    <t>interCompanyPayable</t>
-  </si>
-  <si>
-    <t>col52</t>
-  </si>
-  <si>
-    <t>一年内到期的非流动负债</t>
-  </si>
-  <si>
-    <t>noncurrentLiabilitiesDueWithinOneYear</t>
-  </si>
-  <si>
-    <t>col53</t>
-  </si>
-  <si>
-    <t>其他流动负债</t>
-  </si>
-  <si>
-    <t>otherCurrentLiabilities</t>
-  </si>
-  <si>
-    <t>col54</t>
-  </si>
-  <si>
-    <t>流动负债合计</t>
-  </si>
-  <si>
-    <t>totalCurrentLiabilities</t>
-  </si>
-  <si>
-    <t>col55</t>
-  </si>
-  <si>
-    <t>长期借款</t>
-  </si>
-  <si>
-    <t>longTermLoans</t>
-  </si>
-  <si>
-    <t>col56</t>
-  </si>
-  <si>
-    <t>应付债券</t>
-  </si>
-  <si>
-    <t>bondsPayable</t>
-  </si>
-  <si>
-    <t>col57</t>
-  </si>
-  <si>
-    <t>长期应付款</t>
-  </si>
-  <si>
-    <t>longTermPayable</t>
-  </si>
-  <si>
-    <t>col58</t>
-  </si>
-  <si>
-    <t>专项应付款</t>
-  </si>
-  <si>
-    <t>specialPayable</t>
-  </si>
-  <si>
-    <t>col59</t>
-  </si>
-  <si>
-    <t>预计负债</t>
-  </si>
-  <si>
-    <t>estimatedLiabilities</t>
-  </si>
-  <si>
-    <t>col60</t>
-  </si>
-  <si>
-    <t>递延所得税负债</t>
-  </si>
-  <si>
-    <t>defferredIncomeTaxLiabilities</t>
-  </si>
-  <si>
-    <t>col61</t>
-  </si>
-  <si>
-    <t>其他非流动负债</t>
-  </si>
-  <si>
-    <t>otherNonCurrentLiabilities</t>
-  </si>
-  <si>
-    <t>col62</t>
-  </si>
-  <si>
-    <t>非流动负债合计</t>
-  </si>
-  <si>
-    <t>totalNonCurrentLiabilities</t>
-  </si>
-  <si>
-    <t>col63</t>
-  </si>
-  <si>
-    <t>负债合计</t>
-  </si>
-  <si>
-    <t>totalLiabilities</t>
-  </si>
-  <si>
-    <t>col64</t>
-  </si>
-  <si>
-    <t>实收资本（或股本）</t>
-  </si>
-  <si>
-    <t>totalShare</t>
-  </si>
-  <si>
-    <t>col65</t>
-  </si>
-  <si>
-    <t>资本公积</t>
-  </si>
-  <si>
-    <t>capitalReserve</t>
-  </si>
-  <si>
-    <t>col66</t>
-  </si>
-  <si>
-    <t>盈余公积</t>
-  </si>
-  <si>
-    <t>surplusReserve</t>
-  </si>
-  <si>
-    <t>col67</t>
-  </si>
-  <si>
-    <t>减：库存股</t>
-  </si>
-  <si>
-    <t>treasuryStock</t>
-  </si>
-  <si>
-    <t>col68</t>
-  </si>
-  <si>
-    <t>未分配利润</t>
-  </si>
-  <si>
-    <t>undistributedProfits</t>
-  </si>
-  <si>
-    <t>col69</t>
-  </si>
-  <si>
-    <t>少数股东权益</t>
-  </si>
-  <si>
-    <t>minorityEquity</t>
-  </si>
-  <si>
-    <t>col70</t>
-  </si>
-  <si>
-    <t>外币报表折算价差</t>
-  </si>
-  <si>
-    <t>foreignCurrencyReportTranslationSpread</t>
-  </si>
-  <si>
-    <t>col71</t>
-  </si>
-  <si>
-    <t>非正常经营项目收益调整</t>
-  </si>
-  <si>
-    <t>abnormalBusinessProjectEarningsAdjustment</t>
-  </si>
-  <si>
-    <t>col72</t>
-  </si>
-  <si>
-    <t>所有者权益（或股东权益）合计</t>
-  </si>
-  <si>
-    <t>totalOwnersEquity</t>
-  </si>
-  <si>
-    <t>col73</t>
-  </si>
-  <si>
-    <t>负债和所有者（或股东权益）合计</t>
-  </si>
-  <si>
-    <t>totalLiabilitiesAndOwnersEquity</t>
-  </si>
-  <si>
-    <t>col74</t>
-  </si>
-  <si>
-    <t>其中：营业收入</t>
-  </si>
-  <si>
-    <t>operatingRevenue</t>
-  </si>
-  <si>
-    <t>col75</t>
-  </si>
-  <si>
-    <t>其中：营业成本</t>
-  </si>
-  <si>
-    <t>operatingCosts</t>
-  </si>
-  <si>
-    <t>col76</t>
-  </si>
-  <si>
-    <t>营业税金及附加</t>
-  </si>
-  <si>
-    <t>taxAndSurcharges</t>
-  </si>
-  <si>
-    <t>col77</t>
-  </si>
-  <si>
-    <t>销售费用</t>
-  </si>
-  <si>
-    <t>salesCosts</t>
-  </si>
-  <si>
-    <t>col78</t>
-  </si>
-  <si>
-    <t>管理费用</t>
-  </si>
-  <si>
-    <t>managementCosts</t>
-  </si>
-  <si>
-    <t>col79</t>
-  </si>
-  <si>
-    <t>堪探费用</t>
-  </si>
-  <si>
-    <t>explorationCosts</t>
-  </si>
-  <si>
-    <t>col80</t>
-  </si>
-  <si>
-    <t>财务费用（利润表）</t>
-  </si>
-  <si>
-    <t>financialCosts</t>
-  </si>
-  <si>
-    <t>col81</t>
-  </si>
-  <si>
-    <t>资产减值损失（元）</t>
-  </si>
-  <si>
-    <t>assestsDevaluation</t>
-  </si>
-  <si>
-    <t>col82</t>
-  </si>
-  <si>
-    <t>加：公允价值变动净收益</t>
-  </si>
-  <si>
-    <t>profitAndLossFromFairValueChanges</t>
-  </si>
-  <si>
-    <t>col83</t>
-  </si>
-  <si>
-    <t>投资收益</t>
-  </si>
-  <si>
-    <t>investmentIncome</t>
-  </si>
-  <si>
-    <t>col84</t>
-  </si>
-  <si>
-    <t>其中：对联营企业和合营企业的投资收益</t>
-  </si>
-  <si>
-    <t>investmentIncomeFromAffiliatedBusinessAndCooperativeEnterprise</t>
-  </si>
-  <si>
-    <t>col85</t>
-  </si>
-  <si>
-    <t>影响营业利润的其他科目</t>
-  </si>
-  <si>
-    <t>otherSubjectsAffectingOperatingProfit</t>
-  </si>
-  <si>
-    <t>col86</t>
-  </si>
-  <si>
-    <t>营业利润</t>
-  </si>
-  <si>
-    <t>operatingProfit</t>
-  </si>
-  <si>
-    <t>col87</t>
-  </si>
-  <si>
-    <t>加：补贴收入</t>
-  </si>
-  <si>
-    <t>subsidyIncome</t>
-  </si>
-  <si>
-    <t>col88</t>
-  </si>
-  <si>
-    <t>营业外收入</t>
-  </si>
-  <si>
-    <t>nonOperatingIncome</t>
-  </si>
-  <si>
-    <t>col89</t>
-  </si>
-  <si>
-    <t>减：营业外支出</t>
-  </si>
-  <si>
-    <t>nonOperatingExpenses</t>
-  </si>
-  <si>
-    <t>col90</t>
-  </si>
-  <si>
-    <t>其中：非流动资产处置净损失</t>
-  </si>
-  <si>
-    <t>netLossFromDisposalOfNonCurrentAssets</t>
-  </si>
-  <si>
-    <t>col91</t>
-  </si>
-  <si>
-    <t>加：影响利润总额的其他科目</t>
-  </si>
-  <si>
-    <t>otherSubjectsAffectTotalProfit</t>
-  </si>
-  <si>
-    <t>col92</t>
-  </si>
-  <si>
-    <t>利润总额</t>
-  </si>
-  <si>
-    <t>totalProfit</t>
-  </si>
-  <si>
-    <t>col93</t>
-  </si>
-  <si>
-    <t>减：所得税</t>
-  </si>
-  <si>
-    <t>incomeTax</t>
-  </si>
-  <si>
-    <t>col94</t>
-  </si>
-  <si>
-    <t>加：影响净利润的其他科目</t>
-  </si>
-  <si>
-    <t>otherSubjectsAffectNetProfit</t>
-  </si>
-  <si>
-    <t>col95</t>
-  </si>
-  <si>
-    <t>净利润（利润表=134）</t>
-  </si>
-  <si>
-    <t>netProfit</t>
-  </si>
-  <si>
-    <t>col96</t>
-  </si>
-  <si>
-    <t>归属于母公司所有者的净利润</t>
-  </si>
-  <si>
-    <t>netProfitsBelongToParentCompanyOwner</t>
-  </si>
-  <si>
-    <t>col97</t>
-  </si>
-  <si>
-    <t>少数股东损益</t>
-  </si>
-  <si>
-    <t>minorityProfitAndLoss</t>
-  </si>
-  <si>
-    <t>col98</t>
-  </si>
-  <si>
-    <t>销售商品、提供劳务收到的现金</t>
-  </si>
-  <si>
-    <t>cashFromGoodsSalesorOrRenderingOfServices</t>
-  </si>
-  <si>
-    <t>col99</t>
-  </si>
-  <si>
-    <t>收到的税费返还</t>
-  </si>
-  <si>
-    <t>refundOfTaxAndFeeReceived</t>
-  </si>
-  <si>
-    <t>col100</t>
-  </si>
-  <si>
-    <t>收到其他与经营活动有关的现金</t>
-  </si>
-  <si>
-    <t>otherCashRelatedBusinessActivitiesReceived</t>
-  </si>
-  <si>
-    <t>col101</t>
-  </si>
-  <si>
-    <t>经营活动现金流入小计</t>
-  </si>
-  <si>
-    <t>cashInflowsFromOperatingActivities</t>
-  </si>
-  <si>
-    <t>col102</t>
-  </si>
-  <si>
-    <t>购买商品、接受劳务支付的现金</t>
-  </si>
-  <si>
-    <t>buyingGoodsReceivingCashPaidForLabor</t>
-  </si>
-  <si>
-    <t>col103</t>
-  </si>
-  <si>
-    <t>支付给职工以及为职工支付的现金</t>
-  </si>
-  <si>
-    <t>paymentToEmployeesAndCashPaidForEmployees</t>
-  </si>
-  <si>
-    <t>col104</t>
-  </si>
-  <si>
-    <t>支付的各项税费</t>
-  </si>
-  <si>
-    <t>paymentsOfVariousTaxes</t>
-  </si>
-  <si>
-    <t>col105</t>
-  </si>
-  <si>
-    <t>支付其他与经营活动有关的现金</t>
-  </si>
-  <si>
-    <t>paymentOfOtherCashRelatedToBusinessActivities</t>
-  </si>
-  <si>
-    <t>col106</t>
-  </si>
-  <si>
-    <t>经营活动现金流出小计</t>
-  </si>
-  <si>
-    <t>cashOutflowsFromOperatingActivities</t>
-  </si>
-  <si>
-    <t>col107</t>
-  </si>
-  <si>
-    <t>经营活动产生的现金流量净额（现金流量=150）</t>
-  </si>
-  <si>
-    <t>netCashFlowsFromOperatingActivities</t>
-  </si>
-  <si>
-    <t>col108</t>
-  </si>
-  <si>
-    <t>收回投资收到的现金</t>
-  </si>
-  <si>
-    <t>cashReceivedFromInvestmentReceived</t>
-  </si>
-  <si>
-    <t>col109</t>
-  </si>
-  <si>
-    <t>取得投资收益收到的现金</t>
-  </si>
-  <si>
-    <t>cashReceivedFromInvestmentIncome</t>
-  </si>
-  <si>
-    <t>col110</t>
-  </si>
-  <si>
-    <t>处置固定资产、无形资产和其他长期资产收回的现金净额</t>
-  </si>
-  <si>
-    <t>disposalOfNetCashForRecoveryOfFixedAssetsIntangibleAssetsAndOtherLongTermAssets</t>
-  </si>
-  <si>
-    <t>col111</t>
-  </si>
-  <si>
-    <t>处置子公司及其他营业单位收到的现金净额</t>
-  </si>
-  <si>
-    <t>disposalOfNetCashReceivedFromSubsidiariesAndOtherBusinessUnits</t>
-  </si>
-  <si>
-    <t>col112</t>
-  </si>
-  <si>
-    <t>收到其他与投资活动有关的现金</t>
-  </si>
-  <si>
-    <t>otherCashReceivedRelatingToInvestingActivities</t>
-  </si>
-  <si>
-    <t>col113</t>
-  </si>
-  <si>
-    <t>投资活动现金流入小计</t>
-  </si>
-  <si>
-    <t>cashinFlowsFromInvestmentActivities</t>
-  </si>
-  <si>
-    <t>col114</t>
-  </si>
-  <si>
-    <t>购建固定资产、无形资产和其他长期资产支付的现金</t>
-  </si>
-  <si>
-    <t>cashForThePurchaseConstructionPaymentOfFixedAssetsIntangibleAssetsAndOtherLongTermAssets</t>
-  </si>
-  <si>
-    <t>col115</t>
-  </si>
-  <si>
-    <t>投资支付的现金</t>
-  </si>
-  <si>
-    <t>cashInvestment</t>
-  </si>
-  <si>
-    <t>col116</t>
-  </si>
-  <si>
-    <t>取得子公司及其他营业单位支付的现金净额</t>
-  </si>
-  <si>
-    <t>acquisitionOfNetCashPaidBySubsidiariesAndOtherBusinessUnits</t>
-  </si>
-  <si>
-    <t>col117</t>
-  </si>
-  <si>
-    <t>支付其他与投资活动有关的现金</t>
-  </si>
-  <si>
-    <t>otherCashPaidRelatingToInvestingActivities</t>
-  </si>
-  <si>
-    <t>col118</t>
-  </si>
-  <si>
-    <t>投资活动现金流出小计</t>
-  </si>
-  <si>
-    <t>cashOutflowsFromInvestmentActivities</t>
-  </si>
-  <si>
-    <t>col119</t>
-  </si>
-  <si>
-    <t>投资活动产生的现金流量净额</t>
-  </si>
-  <si>
-    <t>netCashFlowsFromInvestingActivities</t>
-  </si>
-  <si>
-    <t>col120</t>
-  </si>
-  <si>
-    <t>吸收投资收到的现金</t>
-  </si>
-  <si>
-    <t>cashReceivedFromInvestors</t>
-  </si>
-  <si>
-    <t>col121</t>
-  </si>
-  <si>
-    <t>取得借款收到的现金</t>
-  </si>
-  <si>
-    <t>cashFromBorrowings</t>
-  </si>
-  <si>
-    <t>col122</t>
-  </si>
-  <si>
-    <t>收到其他与筹资活动有关的现金</t>
-  </si>
-  <si>
-    <t>otherCashReceivedRelatingToFinancingActivities</t>
-  </si>
-  <si>
-    <t>col123</t>
-  </si>
-  <si>
-    <t>筹资活动现金流入小计</t>
-  </si>
-  <si>
-    <t>cashInflowsFromFinancingActivities</t>
-  </si>
-  <si>
-    <t>col124</t>
-  </si>
-  <si>
-    <t>偿还债务支付的现金</t>
-  </si>
-  <si>
-    <t>cashPaymentsOfAmountBorrowed</t>
-  </si>
-  <si>
-    <t>col125</t>
-  </si>
-  <si>
-    <t>分配股利、利润或偿付利息支付的现金</t>
-  </si>
-  <si>
-    <t>cashPaymentsForDistrbutionOfDividendsOrProfits</t>
-  </si>
-  <si>
-    <t>col126</t>
-  </si>
-  <si>
-    <t>支付其他与筹资活动有关的现金</t>
-  </si>
-  <si>
-    <t>otherCashPaymentRelatingToFinancingActivities</t>
-  </si>
-  <si>
-    <t>col127</t>
-  </si>
-  <si>
-    <t>筹资活动现金流出小计</t>
-  </si>
-  <si>
-    <t>cashOutflowsFromFinancingActivities</t>
-  </si>
-  <si>
-    <t>col128</t>
-  </si>
-  <si>
-    <t>筹资活动产生的现金流量净额</t>
-  </si>
-  <si>
-    <t>netCashFlowsFromFinancingActivities</t>
-  </si>
-  <si>
-    <t>col129</t>
-  </si>
-  <si>
-    <t>汇率变动对现金的影响</t>
-  </si>
-  <si>
-    <t>effectOfForeignExchangRateChangesOnCash</t>
-  </si>
-  <si>
-    <t>col130</t>
-  </si>
-  <si>
-    <t>其他原因对现金的影响（汇率变动）</t>
-  </si>
-  <si>
-    <t>effectOfOtherReasonOnCash</t>
-  </si>
-  <si>
-    <t>col131</t>
-  </si>
-  <si>
-    <t>现金及现金等价物净增加额（158）</t>
-  </si>
-  <si>
-    <t>netIncreaseInCashAndCashEquivalents</t>
-  </si>
-  <si>
-    <t>col132</t>
-  </si>
-  <si>
-    <t>期初现金及现金等价物余额</t>
-  </si>
-  <si>
-    <t>initialCashAndCashEquivalentsBalance</t>
-  </si>
-  <si>
-    <t>col133</t>
-  </si>
-  <si>
-    <t>期末现金及现金等价物余额</t>
-  </si>
-  <si>
-    <t>theFinalCashAndCashEquivalentsBalance</t>
-  </si>
-  <si>
-    <t>col134</t>
-  </si>
-  <si>
-    <t>净利润（现金流量附表=95）</t>
-  </si>
-  <si>
-    <t>netProfitFromOperatingActivities</t>
-  </si>
-  <si>
-    <t>col135</t>
-  </si>
-  <si>
-    <t>资产减值准备（元）</t>
-  </si>
-  <si>
-    <t>provisionForAssetsLosses</t>
-  </si>
-  <si>
-    <t>col136</t>
-  </si>
-  <si>
-    <t>固定资产折旧、油气资产折耗、生产性生物资产折旧</t>
-  </si>
-  <si>
-    <t>depreciationForFixedAssets</t>
-  </si>
-  <si>
-    <t>col137</t>
-  </si>
-  <si>
-    <t>无形资产摊销</t>
-  </si>
-  <si>
-    <t>amortizationOfIntangibleAssets</t>
-  </si>
-  <si>
-    <t>col138</t>
-  </si>
-  <si>
-    <t>长期待摊费用摊销</t>
-  </si>
-  <si>
-    <t>amortizationOfLong-termDeferredExpenses</t>
-  </si>
-  <si>
-    <t>col139</t>
-  </si>
-  <si>
-    <t>处置固定资产、无形资产和其他长期资产的损失</t>
-  </si>
-  <si>
-    <t>lossOfDisposingFixedAssetsIntangibleAssetsAndOtherLong-termAssets</t>
-  </si>
-  <si>
-    <t>col140</t>
-  </si>
-  <si>
-    <t>固定资产报废损失</t>
-  </si>
-  <si>
-    <t>scrapLossOfFixedAssets</t>
-  </si>
-  <si>
-    <t>col141</t>
-  </si>
-  <si>
-    <t>公允价值变动损失</t>
-  </si>
-  <si>
-    <t>lossFromFairValueChange</t>
-  </si>
-  <si>
-    <t>col142</t>
-  </si>
-  <si>
-    <t>财务费用（现金流量表）</t>
-  </si>
-  <si>
-    <t>financialExpenses</t>
-  </si>
-  <si>
-    <t>col143</t>
-  </si>
-  <si>
-    <t>投资损失</t>
-  </si>
-  <si>
-    <t>investmentLosses</t>
-  </si>
-  <si>
-    <t>col144</t>
-  </si>
-  <si>
-    <t>递延所得税资产减少</t>
-  </si>
-  <si>
-    <t>decreaseOfDeferredTaxAssets</t>
-  </si>
-  <si>
-    <t>col145</t>
-  </si>
-  <si>
-    <t>递延所得税负债增加</t>
-  </si>
-  <si>
-    <t>increaseOfDeferredTaxLiabilities</t>
-  </si>
-  <si>
-    <t>col146</t>
-  </si>
-  <si>
-    <t>存货的减少</t>
-  </si>
-  <si>
-    <t>decreaseOfInventory</t>
-  </si>
-  <si>
-    <t>col147</t>
-  </si>
-  <si>
-    <t>经营性应收项目的减少</t>
-  </si>
-  <si>
-    <t>decreaseOfOperationReceivables</t>
-  </si>
-  <si>
-    <t>col148</t>
-  </si>
-  <si>
-    <t>经营性应付项目的增加</t>
-  </si>
-  <si>
-    <t>increaseOfOperationPayables</t>
-  </si>
-  <si>
-    <t>col150</t>
-  </si>
-  <si>
-    <t>经营活动产生的现金流量净额（现金流量附表=107）</t>
-  </si>
-  <si>
-    <t>netCashFromOperatingActivities2</t>
-  </si>
-  <si>
-    <t>col151</t>
-  </si>
-  <si>
-    <t>债务转为资本</t>
-  </si>
-  <si>
-    <t>debtConvertedToCSapital</t>
-  </si>
-  <si>
-    <t>col152</t>
-  </si>
-  <si>
-    <t>一年内到期的可转换公司债券</t>
-  </si>
-  <si>
-    <t>convertibleBondMaturityWithinOneYear</t>
-  </si>
-  <si>
-    <t>col153</t>
-  </si>
-  <si>
-    <t>融资租入固定资产</t>
-  </si>
-  <si>
-    <t>leaseholdImprovements</t>
-  </si>
-  <si>
-    <t>col154</t>
-  </si>
-  <si>
-    <t>现金的期末余额</t>
-  </si>
-  <si>
-    <t>cashEndingBal</t>
-  </si>
-  <si>
-    <t>col155</t>
-  </si>
-  <si>
-    <t>现金的期初余额</t>
-  </si>
-  <si>
-    <t>cashBeginingBal</t>
-  </si>
-  <si>
-    <t>col156</t>
-  </si>
-  <si>
-    <t>现金等价物的期末余额</t>
-  </si>
-  <si>
-    <t>cashEquivalentsEndingBal</t>
-  </si>
-  <si>
-    <t>col157</t>
-  </si>
-  <si>
-    <t>现金等价物的期初余额</t>
-  </si>
-  <si>
-    <t>cashEquivalentsBeginningBal</t>
-  </si>
-  <si>
-    <t>col158</t>
-  </si>
-  <si>
-    <t>现金及现金等价物净增加额（131）</t>
-  </si>
-  <si>
-    <t>netIncreaseOfCashAndCashEquivalents</t>
-  </si>
-  <si>
-    <t>col159</t>
-  </si>
-  <si>
-    <t>流动比率</t>
-  </si>
-  <si>
-    <t>currentRatio  # 流动资产/流动负债</t>
-  </si>
-  <si>
-    <t>col160</t>
-  </si>
-  <si>
-    <t>速动比率</t>
-  </si>
-  <si>
-    <t>acidTestRatio  # (流动资产-存货）/流动负债</t>
-  </si>
-  <si>
-    <t>col161</t>
-  </si>
-  <si>
-    <t>现金比率(%)</t>
-  </si>
-  <si>
-    <t>cashRatio  # (货币资金+有价证券)÷流动负债</t>
-  </si>
-  <si>
-    <t>col162</t>
-  </si>
-  <si>
-    <t>利息保障倍数</t>
-  </si>
-  <si>
-    <t>interestCoverageRatio  # (利润总额+财务费用（仅指利息费用部份）)/利息费用</t>
-  </si>
-  <si>
-    <t>col163</t>
-  </si>
-  <si>
-    <t>非流动负债比率(%)</t>
-  </si>
-  <si>
-    <t>noncurrentLiabilitiesRatio</t>
-  </si>
-  <si>
-    <t>col164</t>
-  </si>
-  <si>
-    <t>流动负债比率(%)</t>
-  </si>
-  <si>
-    <t>currentLiabilitiesRatio</t>
-  </si>
-  <si>
-    <t>col165</t>
-  </si>
-  <si>
-    <t>现金到期债务比率(%)</t>
-  </si>
-  <si>
-    <t>cashDebtRatio  # 企业经营现金净流入/(本期到期长期负债+本期应付票据)</t>
-  </si>
-  <si>
-    <t>col166</t>
-  </si>
-  <si>
-    <t>有形资产净值债务率(%)</t>
-  </si>
-  <si>
-    <t>debtToTangibleAssetsRatio</t>
-  </si>
-  <si>
-    <t>col167</t>
-  </si>
-  <si>
-    <t>权益乘数(%)</t>
-  </si>
-  <si>
-    <t>equityMultiplier  # 资产总额/股东权益总额</t>
-  </si>
-  <si>
-    <t>col168</t>
-  </si>
-  <si>
-    <t>股东的权益/负债合计(%)</t>
-  </si>
-  <si>
-    <t>equityDebtRatio  # 权益负债率</t>
-  </si>
-  <si>
-    <t>col169</t>
-  </si>
-  <si>
-    <t>有形资产/负债合计(%)</t>
-  </si>
-  <si>
-    <t>tangibleAssetDebtRatio   # 有形资产负债率</t>
-  </si>
-  <si>
-    <t>col170</t>
-  </si>
-  <si>
-    <t>经营活动产生的现金流量净额/负债合计(%)</t>
-  </si>
-  <si>
-    <t>netCashFlowsFromOperatingActivitiesDebtRatio</t>
-  </si>
-  <si>
-    <t>col171</t>
-  </si>
-  <si>
-    <t>税息折旧及摊销前利润/负债合计(%)</t>
-  </si>
-  <si>
-    <t>EBITDA/Liabilities</t>
-  </si>
-  <si>
-    <t>col172</t>
-  </si>
-  <si>
-    <t>应收帐款周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfReceivable</t>
-  </si>
-  <si>
-    <t>col173</t>
-  </si>
-  <si>
-    <t>存货周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfInventory</t>
-  </si>
-  <si>
-    <t>col174</t>
-  </si>
-  <si>
-    <t>运营资金周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfOperatingAssets</t>
-  </si>
-  <si>
-    <t>col175</t>
-  </si>
-  <si>
-    <t>总资产周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfTotalAssets</t>
-  </si>
-  <si>
-    <t>col176</t>
-  </si>
-  <si>
-    <t>固定资产周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfFixedAssets  # 企业销售收入与固定资产净值的比率</t>
-  </si>
-  <si>
-    <t>col177</t>
-  </si>
-  <si>
-    <t>应收帐款周转天数</t>
-  </si>
-  <si>
-    <t>daysSalesOutstanding  # 企业从取得应收账款的权利到收回款项、转换为现金所需要的时间</t>
-  </si>
-  <si>
-    <t>col178</t>
-  </si>
-  <si>
-    <t>存货周转天数</t>
-  </si>
-  <si>
-    <t>daysSalesOfInventory  # 企业从取得存货开始至消耗、销售为止所经历的天数</t>
-  </si>
-  <si>
-    <t>col179</t>
-  </si>
-  <si>
-    <t>流动资产周转率</t>
-  </si>
-  <si>
-    <t>turnoverRatioOfCurrentAssets  # 流动资产周转率(次)=主营业务收入/平均流动资产总额</t>
-  </si>
-  <si>
-    <t>col180</t>
-  </si>
-  <si>
-    <t>流动资产周转天数</t>
-  </si>
-  <si>
-    <t>daysSalesofCurrentAssets</t>
-  </si>
-  <si>
-    <t>col181</t>
-  </si>
-  <si>
-    <t>总资产周转天数</t>
-  </si>
-  <si>
-    <t>daysSalesofTotalAssets</t>
-  </si>
-  <si>
-    <t>col182</t>
-  </si>
-  <si>
-    <t>股东权益周转率</t>
-  </si>
-  <si>
-    <t>equityTurnover  # 销售收入/平均股东权益</t>
-  </si>
-  <si>
-    <t>col183</t>
-  </si>
-  <si>
-    <t>营业收入增长率(%)</t>
-  </si>
-  <si>
-    <t>operatingIncomeGrowth</t>
-  </si>
-  <si>
-    <t>col184</t>
-  </si>
-  <si>
-    <t>净利润增长率(%)</t>
-  </si>
-  <si>
-    <t>netProfitGrowthRate  # NPGR  利润总额－所得税</t>
-  </si>
-  <si>
-    <t>col185</t>
-  </si>
-  <si>
-    <t>净资产增长率(%)</t>
-  </si>
-  <si>
-    <t>netAssetsGrowthRate</t>
-  </si>
-  <si>
-    <t>col186</t>
-  </si>
-  <si>
-    <t>固定资产增长率(%)</t>
-  </si>
-  <si>
-    <t>fixedAssetsGrowthRate</t>
-  </si>
-  <si>
-    <t>col187</t>
-  </si>
-  <si>
-    <t>总资产增长率(%)</t>
-  </si>
-  <si>
-    <t>totalAssetsGrowthRate</t>
-  </si>
-  <si>
-    <t>col188</t>
-  </si>
-  <si>
-    <t>投资收益增长率(%)</t>
-  </si>
-  <si>
-    <t>investmentIncomeGrowthRate</t>
-  </si>
-  <si>
-    <t>col189</t>
-  </si>
-  <si>
-    <t>营业利润增长率(%)</t>
-  </si>
-  <si>
-    <t>operatingProfitGrowthRate</t>
-  </si>
-  <si>
-    <t>col193</t>
-  </si>
-  <si>
-    <t>成本费用利润率(%)</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnCost</t>
-  </si>
-  <si>
-    <t>col194</t>
-  </si>
-  <si>
-    <t>营业利润率</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnOperatingProfit</t>
-  </si>
-  <si>
-    <t>col195</t>
-  </si>
-  <si>
-    <t>营业税金率</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnBusinessTax</t>
-  </si>
-  <si>
-    <t>col196</t>
-  </si>
-  <si>
-    <t>营业成本率</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnOperatingCost</t>
-  </si>
-  <si>
-    <t>col197</t>
-  </si>
-  <si>
-    <t>净资产收益率（获利能力分析=6）</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnCommonStockholdersEquity</t>
-  </si>
-  <si>
-    <t>col198</t>
-  </si>
-  <si>
-    <t>投资收益率</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnInvestmentIncome</t>
-  </si>
-  <si>
-    <t>col199</t>
-  </si>
-  <si>
-    <t>销售净利率(%)</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnNetSalesProfit</t>
-  </si>
-  <si>
-    <t>col200</t>
-  </si>
-  <si>
-    <t>总资产报酬率</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnTotalAssets</t>
-  </si>
-  <si>
-    <t>col201</t>
-  </si>
-  <si>
-    <t>净利润率</t>
-  </si>
-  <si>
-    <t>netProfitMargin</t>
-  </si>
-  <si>
-    <t>col202</t>
-  </si>
-  <si>
-    <t>销售毛利率(%)</t>
-  </si>
-  <si>
-    <t>rateOfReturnOnGrossProfitFromSales</t>
-  </si>
-  <si>
-    <t>col203</t>
-  </si>
-  <si>
-    <t>三费比重</t>
-  </si>
-  <si>
-    <t>threeFeeProportion</t>
-  </si>
-  <si>
-    <t>col204</t>
-  </si>
-  <si>
-    <t>管理费用率</t>
-  </si>
-  <si>
-    <t>ratioOfChargingExpense</t>
-  </si>
-  <si>
-    <t>col205</t>
-  </si>
-  <si>
-    <t>财务费用率</t>
-  </si>
-  <si>
-    <t>ratioOfFinancialExpense</t>
-  </si>
-  <si>
-    <t>col206</t>
-  </si>
-  <si>
-    <t>扣除非经常性损益后的净利润</t>
-  </si>
-  <si>
-    <t>netProfitAfterExtraordinaryGainsAndLosses</t>
-  </si>
-  <si>
-    <t>col207</t>
-  </si>
-  <si>
-    <t>息税前利润(EBIT)</t>
-  </si>
-  <si>
-    <t>EBIT</t>
-  </si>
-  <si>
-    <t>col208</t>
-  </si>
-  <si>
-    <t>息税折旧摊销前利润(EBITDA)</t>
-  </si>
-  <si>
-    <t>EBITDA</t>
-  </si>
-  <si>
-    <t>col209</t>
-  </si>
-  <si>
-    <t>EBITDA/营业总收入(%)</t>
-  </si>
-  <si>
-    <t>EBITDA/GrossRevenueRate</t>
-  </si>
-  <si>
-    <t>col210</t>
-  </si>
-  <si>
-    <t>资产负债率(%)</t>
-  </si>
-  <si>
-    <t>assetsLiabilitiesRatio</t>
-  </si>
-  <si>
-    <t>col211</t>
-  </si>
-  <si>
-    <t>流动资产比率</t>
-  </si>
-  <si>
-    <t>currentAssetsRatio  # 期末的流动资产除以所有者权益</t>
-  </si>
-  <si>
-    <t>col212</t>
-  </si>
-  <si>
-    <t>货币资金比率</t>
-  </si>
-  <si>
-    <t>monetaryFundRatio</t>
-  </si>
-  <si>
-    <t>col213</t>
-  </si>
-  <si>
-    <t>存货比率</t>
-  </si>
-  <si>
-    <t>inventoryRatio</t>
-  </si>
-  <si>
-    <t>col214</t>
-  </si>
-  <si>
-    <t>固定资产比率</t>
-  </si>
-  <si>
-    <t>fixedAssetsRatio</t>
-  </si>
-  <si>
-    <t>col215</t>
-  </si>
-  <si>
-    <t>负债结构比</t>
-  </si>
-  <si>
-    <t>liabilitiesStructureRatio</t>
-  </si>
-  <si>
-    <t>col216</t>
-  </si>
-  <si>
-    <t>归属于母公司股东权益/全部投入资本(%)</t>
-  </si>
-  <si>
-    <t>shareholdersOwnershipOfAParentCompany/TotalCapital</t>
-  </si>
-  <si>
-    <t>col217</t>
-  </si>
-  <si>
-    <t>股东的权益/带息债务(%)</t>
-  </si>
-  <si>
-    <t>shareholdersInterest/InterestRateDebtRatio</t>
-  </si>
-  <si>
-    <t>col218</t>
-  </si>
-  <si>
-    <t>有形资产/净债务(%)</t>
-  </si>
-  <si>
-    <t>tangibleAssets/NetDebtRatio</t>
-  </si>
-  <si>
-    <t>col219</t>
-  </si>
-  <si>
-    <t>每股经营现金流（现金流量分析=7）</t>
-  </si>
-  <si>
     <t>col220</t>
   </si>
   <si>
-    <t>营业收入现金含量(%)</t>
+    <t>营业收入现金含量</t>
   </si>
   <si>
     <t>cashOfOperatingIncome</t>
@@ -1978,7 +1993,7 @@
     <t>col221</t>
   </si>
   <si>
-    <t>经营活动产生的现金流量净额/经营活动净收益(%)</t>
+    <t>经营活动产生的现金流量净额/经营活动净收益</t>
   </si>
   <si>
     <t>netOperatingCashFlow/netOperationProfit</t>
@@ -1987,7 +2002,7 @@
     <t>col222</t>
   </si>
   <si>
-    <t>销售商品提供劳务收到的现金/营业收入(%)</t>
+    <t>销售商品提供劳务收到的现金/营业收入</t>
   </si>
   <si>
     <t>cashFromGoodsSales/OperatingRevenue</t>
@@ -2533,7 +2548,7 @@
     <t>col283</t>
   </si>
   <si>
-    <t>最近一年营业收入()</t>
+    <t>最近一年营业收入</t>
   </si>
   <si>
     <t>lastYearOperatingIncome</t>
@@ -2551,7 +2566,7 @@
     <t>col285</t>
   </si>
   <si>
-    <t>业绩预告-本期净利润同比增幅下限%</t>
+    <t>业绩预告-本期净利润同比增幅下限</t>
   </si>
   <si>
     <t>PF_theLowerLimitoftheYearonyearGrowthofNetProfitForThePeriod</t>
@@ -2560,7 +2575,7 @@
     <t>col286</t>
   </si>
   <si>
-    <t>业绩预告-本期净利润同比增幅上限%</t>
+    <t>业绩预告-本期净利润同比增幅上限</t>
   </si>
   <si>
     <t>PF_theHigherLimitoftheYearonyearGrowthofNetProfitForThePeriod</t>
@@ -2890,6 +2905,12 @@
     <t>Free cash flow per share for shareholders</t>
   </si>
   <si>
+    <t>col326</t>
+  </si>
+  <si>
+    <t>香港中央结算有限公司持股</t>
+  </si>
+  <si>
     <t>col401</t>
   </si>
   <si>
@@ -2929,7 +2950,7 @@
     <t>col405</t>
   </si>
   <si>
-    <t>衍生金融资产</t>
+    <t>衍生金融资产（万元）</t>
   </si>
   <si>
     <t>Derivative financial assets</t>
@@ -3016,7 +3037,7 @@
     <t>col415</t>
   </si>
   <si>
-    <t>衍生金融负债</t>
+    <t>衍生金融负债（万元）</t>
   </si>
   <si>
     <t>Derivative financial liabilities</t>
@@ -3169,7 +3190,7 @@
     <t>col432</t>
   </si>
   <si>
-    <t>其他权益工具投资</t>
+    <t>其他权益工具投资（万元）</t>
   </si>
   <si>
     <t>Investment in other equity instruments</t>
@@ -3178,7 +3199,7 @@
     <t>col433</t>
   </si>
   <si>
-    <t>其他非流动金融资产</t>
+    <t>其他非流动金融资产（万元）</t>
   </si>
   <si>
     <t>Other non-current financial assets</t>
@@ -3187,7 +3208,7 @@
     <t>col434</t>
   </si>
   <si>
-    <t>合同负债</t>
+    <t>合同负债（万元）</t>
   </si>
   <si>
     <t>Contract liabilities</t>
@@ -3196,7 +3217,7 @@
     <t>col435</t>
   </si>
   <si>
-    <t>合同资产</t>
+    <t>合同资产（万元）</t>
   </si>
   <si>
     <t>Contract assets</t>
@@ -3223,7 +3244,7 @@
     <t>col438</t>
   </si>
   <si>
-    <t>使用权资产</t>
+    <t>使用权资产（万元）</t>
   </si>
   <si>
     <t>Right-of-use assets</t>
@@ -3232,7 +3253,7 @@
     <t>col439</t>
   </si>
   <si>
-    <t>租赁负债</t>
+    <t>租赁负债（万元）</t>
   </si>
   <si>
     <t>Lease liabilities</t>
@@ -3250,7 +3271,7 @@
     <t>col502</t>
   </si>
   <si>
-    <t>营业总收入</t>
+    <t>营业总收入（万元）</t>
   </si>
   <si>
     <t>Total operating income</t>
@@ -3268,7 +3289,7 @@
     <t>col504</t>
   </si>
   <si>
-    <t>其中归属于母公司综合收益</t>
+    <t>其中归属于母公司综合收益总额（万元）</t>
   </si>
   <si>
     <t>Comprehensive income attributable to parent company</t>
@@ -3277,7 +3298,7 @@
     <t>col505</t>
   </si>
   <si>
-    <t>其中归属于少数股东综合收益</t>
+    <t>其中归属于少数股东综合收益总额（万元）</t>
   </si>
   <si>
     <t>Comprehensive income attributable to minority shareholders</t>
@@ -3403,7 +3424,7 @@
     <t>col519</t>
   </si>
   <si>
-    <t>营业总成本</t>
+    <t>营业总成本（万元）</t>
   </si>
   <si>
     <t>Total operating costs</t>
@@ -3412,13 +3433,13 @@
     <t>col520</t>
   </si>
   <si>
-    <t>信用减值损失（其他经营收益）</t>
+    <t>信用减值损失（其他经营收益）（万元）</t>
   </si>
   <si>
     <t>col521</t>
   </si>
   <si>
-    <t>资产减值损失（其他经营收益 万元）</t>
+    <t>资产减值损失（其他经营收益）（万元）</t>
   </si>
   <si>
     <t>Impairment loss on assets</t>
@@ -3571,7 +3592,7 @@
     <t>col577</t>
   </si>
   <si>
-    <t>其中子公司吸收少数股东投资收到的现金</t>
+    <t>筹资活动子公司吸收少数股东投资收到的现金（万元）</t>
   </si>
   <si>
     <t>cash received from minority shareholders investment in subsidiaries</t>
@@ -3580,7 +3601,7 @@
     <t>col578</t>
   </si>
   <si>
-    <t>其中子公司支付给少数股东的股利利润</t>
+    <t>筹资活动子公司支付给少数股东的股利利润（万元）</t>
   </si>
   <si>
     <t>Dividends and profits paid by subsidiaries to minority shareholders</t>
@@ -3589,7 +3610,7 @@
     <t>col579</t>
   </si>
   <si>
-    <t>投资性房地产的折旧及摊销</t>
+    <t>投资性房地产折旧及摊销（万元）</t>
   </si>
   <si>
     <t>Depreciation and amortization of investment properties</t>
@@ -3598,7 +3619,13 @@
     <t>col580</t>
   </si>
   <si>
-    <t>信用减值损失（损失）</t>
+    <t>信用减值损失（损失）（万元）</t>
+  </si>
+  <si>
+    <t>col581</t>
+  </si>
+  <si>
+    <t>使用权资产折旧/摊销</t>
   </si>
 </sst>
 </file>
@@ -3627,11 +3654,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4096,7 +4121,7 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4105,10 +4130,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4117,7 +4142,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4126,13 +4151,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4241,10 +4266,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4592,7 +4621,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C400"/>
+  <dimension ref="A1:C404"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
@@ -6250,1236 +6279,1230 @@
         <v>449</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:2">
       <c r="A151" s="1" t="s">
         <v>450</v>
       </c>
       <c r="B151" t="s">
         <v>451</v>
       </c>
-      <c r="C151" t="s">
-        <v>452</v>
-      </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B152" t="s">
         <v>453</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>454</v>
-      </c>
-      <c r="C152" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B153" t="s">
         <v>456</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
         <v>457</v>
-      </c>
-      <c r="C153" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B154" t="s">
         <v>459</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>460</v>
-      </c>
-      <c r="C154" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B155" t="s">
         <v>462</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>463</v>
-      </c>
-      <c r="C155" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B156" t="s">
         <v>465</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>466</v>
-      </c>
-      <c r="C156" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B157" t="s">
         <v>468</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>469</v>
-      </c>
-      <c r="C157" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B158" t="s">
         <v>471</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>472</v>
-      </c>
-      <c r="C158" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B159" t="s">
         <v>474</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>475</v>
-      </c>
-      <c r="C159" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B160" t="s">
         <v>477</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C160" t="s">
         <v>478</v>
-      </c>
-      <c r="C160" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B161" t="s">
         <v>480</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
         <v>481</v>
-      </c>
-      <c r="C161" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B162" t="s">
         <v>483</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>484</v>
-      </c>
-      <c r="C162" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B163" t="s">
         <v>486</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>487</v>
-      </c>
-      <c r="C163" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B164" t="s">
         <v>489</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
         <v>490</v>
-      </c>
-      <c r="C164" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B165" t="s">
         <v>492</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>493</v>
-      </c>
-      <c r="C165" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B166" t="s">
         <v>495</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>496</v>
-      </c>
-      <c r="C166" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B167" t="s">
         <v>498</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
         <v>499</v>
-      </c>
-      <c r="C167" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B168" t="s">
         <v>501</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" t="s">
         <v>502</v>
-      </c>
-      <c r="C168" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B169" t="s">
         <v>504</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" t="s">
         <v>505</v>
-      </c>
-      <c r="C169" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B170" t="s">
         <v>507</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" t="s">
         <v>508</v>
-      </c>
-      <c r="C170" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B171" t="s">
         <v>510</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>511</v>
-      </c>
-      <c r="C171" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B172" t="s">
         <v>513</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>514</v>
-      </c>
-      <c r="C172" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B173" t="s">
         <v>516</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>517</v>
-      </c>
-      <c r="C173" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B174" t="s">
         <v>519</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>520</v>
-      </c>
-      <c r="C174" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B175" t="s">
         <v>522</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>523</v>
-      </c>
-      <c r="C175" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B176" t="s">
         <v>525</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>526</v>
-      </c>
-      <c r="C176" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B177" t="s">
         <v>528</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>529</v>
-      </c>
-      <c r="C177" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B178" t="s">
         <v>531</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>532</v>
-      </c>
-      <c r="C178" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B179" t="s">
         <v>534</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>535</v>
-      </c>
-      <c r="C179" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B180" t="s">
         <v>537</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>538</v>
-      </c>
-      <c r="C180" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B181" t="s">
         <v>540</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>541</v>
-      </c>
-      <c r="C181" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B182" t="s">
         <v>543</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>544</v>
-      </c>
-      <c r="C182" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B183" t="s">
         <v>546</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>547</v>
-      </c>
-      <c r="C183" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B184" t="s">
         <v>549</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>550</v>
-      </c>
-      <c r="C184" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B185" t="s">
         <v>552</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>553</v>
-      </c>
-      <c r="C185" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B186" t="s">
         <v>555</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>556</v>
-      </c>
-      <c r="C186" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B187" t="s">
         <v>558</v>
       </c>
-      <c r="B187" t="s">
+      <c r="C187" t="s">
         <v>559</v>
-      </c>
-      <c r="C187" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B188" t="s">
         <v>561</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>562</v>
-      </c>
-      <c r="C188" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B189" t="s">
         <v>564</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>565</v>
-      </c>
-      <c r="C189" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B190" t="s">
         <v>567</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>568</v>
-      </c>
-      <c r="C190" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B191" t="s">
         <v>570</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>571</v>
       </c>
-      <c r="C191" t="s">
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="1" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="1" t="s">
+      <c r="B192" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="B192" t="s">
-        <v>574</v>
-      </c>
-      <c r="C192" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B193" t="s">
+        <v>575</v>
+      </c>
+      <c r="C193" t="s">
         <v>576</v>
-      </c>
-      <c r="B193" t="s">
-        <v>577</v>
-      </c>
-      <c r="C193" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B194" t="s">
+        <v>578</v>
+      </c>
+      <c r="C194" t="s">
         <v>579</v>
-      </c>
-      <c r="B194" t="s">
-        <v>580</v>
-      </c>
-      <c r="C194" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B195" t="s">
+        <v>581</v>
+      </c>
+      <c r="C195" t="s">
         <v>582</v>
-      </c>
-      <c r="B195" t="s">
-        <v>583</v>
-      </c>
-      <c r="C195" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B196" t="s">
+        <v>584</v>
+      </c>
+      <c r="C196" t="s">
         <v>585</v>
-      </c>
-      <c r="B196" t="s">
-        <v>586</v>
-      </c>
-      <c r="C196" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B197" t="s">
+        <v>587</v>
+      </c>
+      <c r="C197" t="s">
         <v>588</v>
-      </c>
-      <c r="B197" t="s">
-        <v>589</v>
-      </c>
-      <c r="C197" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B198" t="s">
+        <v>590</v>
+      </c>
+      <c r="C198" t="s">
         <v>591</v>
-      </c>
-      <c r="B198" t="s">
-        <v>592</v>
-      </c>
-      <c r="C198" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B199" t="s">
+        <v>593</v>
+      </c>
+      <c r="C199" t="s">
         <v>594</v>
-      </c>
-      <c r="B199" t="s">
-        <v>595</v>
-      </c>
-      <c r="C199" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B200" t="s">
+        <v>596</v>
+      </c>
+      <c r="C200" t="s">
         <v>597</v>
-      </c>
-      <c r="B200" t="s">
-        <v>598</v>
-      </c>
-      <c r="C200" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B201" t="s">
+        <v>599</v>
+      </c>
+      <c r="C201" t="s">
         <v>600</v>
-      </c>
-      <c r="B201" t="s">
-        <v>601</v>
-      </c>
-      <c r="C201" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B202" t="s">
+        <v>602</v>
+      </c>
+      <c r="C202" t="s">
         <v>603</v>
-      </c>
-      <c r="B202" t="s">
-        <v>604</v>
-      </c>
-      <c r="C202" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B203" t="s">
+        <v>605</v>
+      </c>
+      <c r="C203" t="s">
         <v>606</v>
-      </c>
-      <c r="B203" t="s">
-        <v>607</v>
-      </c>
-      <c r="C203" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B204" t="s">
+        <v>608</v>
+      </c>
+      <c r="C204" t="s">
         <v>609</v>
-      </c>
-      <c r="B204" t="s">
-        <v>610</v>
-      </c>
-      <c r="C204" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B205" t="s">
+        <v>611</v>
+      </c>
+      <c r="C205" t="s">
         <v>612</v>
-      </c>
-      <c r="B205" t="s">
-        <v>613</v>
-      </c>
-      <c r="C205" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B206" t="s">
+        <v>614</v>
+      </c>
+      <c r="C206" t="s">
         <v>615</v>
-      </c>
-      <c r="B206" t="s">
-        <v>616</v>
-      </c>
-      <c r="C206" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B207" t="s">
+        <v>617</v>
+      </c>
+      <c r="C207" t="s">
         <v>618</v>
-      </c>
-      <c r="B207" t="s">
-        <v>619</v>
-      </c>
-      <c r="C207" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B208" t="s">
+        <v>620</v>
+      </c>
+      <c r="C208" t="s">
         <v>621</v>
-      </c>
-      <c r="B208" t="s">
-        <v>622</v>
-      </c>
-      <c r="C208" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B209" t="s">
+        <v>623</v>
+      </c>
+      <c r="C209" t="s">
         <v>624</v>
-      </c>
-      <c r="B209" t="s">
-        <v>625</v>
-      </c>
-      <c r="C209" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B210" t="s">
+        <v>626</v>
+      </c>
+      <c r="C210" t="s">
         <v>627</v>
-      </c>
-      <c r="B210" t="s">
-        <v>628</v>
-      </c>
-      <c r="C210" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B211" t="s">
+        <v>629</v>
+      </c>
+      <c r="C211" t="s">
         <v>630</v>
-      </c>
-      <c r="B211" t="s">
-        <v>631</v>
-      </c>
-      <c r="C211" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B212" t="s">
+        <v>632</v>
+      </c>
+      <c r="C212" t="s">
         <v>633</v>
-      </c>
-      <c r="B212" t="s">
-        <v>634</v>
-      </c>
-      <c r="C212" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B213" t="s">
+        <v>635</v>
+      </c>
+      <c r="C213" t="s">
         <v>636</v>
-      </c>
-      <c r="B213" t="s">
-        <v>637</v>
-      </c>
-      <c r="C213" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B214" t="s">
+        <v>638</v>
+      </c>
+      <c r="C214" t="s">
         <v>639</v>
-      </c>
-      <c r="B214" t="s">
-        <v>640</v>
-      </c>
-      <c r="C214" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B215" t="s">
+        <v>641</v>
+      </c>
+      <c r="C215" t="s">
         <v>642</v>
-      </c>
-      <c r="B215" t="s">
-        <v>643</v>
-      </c>
-      <c r="C215" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B216" t="s">
+        <v>644</v>
+      </c>
+      <c r="C216" t="s">
         <v>645</v>
-      </c>
-      <c r="B216" t="s">
-        <v>646</v>
-      </c>
-      <c r="C216" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B217" t="s">
+        <v>647</v>
+      </c>
+      <c r="C217" t="s">
         <v>648</v>
-      </c>
-      <c r="B217" t="s">
-        <v>649</v>
-      </c>
-      <c r="C217" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B218" t="s">
         <v>650</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>651</v>
-      </c>
-      <c r="C218" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B219" t="s">
         <v>653</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>654</v>
-      </c>
-      <c r="C219" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B220" t="s">
         <v>656</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>657</v>
-      </c>
-      <c r="C220" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B221" t="s">
         <v>659</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>660</v>
-      </c>
-      <c r="C221" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B222" t="s">
         <v>662</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>663</v>
-      </c>
-      <c r="C222" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B223" t="s">
         <v>665</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>666</v>
-      </c>
-      <c r="C223" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B224" t="s">
         <v>668</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>669</v>
-      </c>
-      <c r="C224" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B225" t="s">
         <v>671</v>
       </c>
-      <c r="B225" t="s">
+      <c r="C225" t="s">
         <v>672</v>
-      </c>
-      <c r="C225" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B226" t="s">
         <v>674</v>
       </c>
-      <c r="B226" t="s">
+      <c r="C226" t="s">
         <v>675</v>
-      </c>
-      <c r="C226" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B227" t="s">
         <v>677</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" t="s">
         <v>678</v>
-      </c>
-      <c r="C227" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B228" t="s">
         <v>680</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>681</v>
-      </c>
-      <c r="C228" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B229" t="s">
         <v>683</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>684</v>
-      </c>
-      <c r="C229" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B230" t="s">
         <v>686</v>
       </c>
-      <c r="B230" t="s">
+      <c r="C230" t="s">
         <v>687</v>
-      </c>
-      <c r="C230" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B231" t="s">
         <v>689</v>
       </c>
-      <c r="B231" t="s">
+      <c r="C231" t="s">
         <v>690</v>
-      </c>
-      <c r="C231" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B232" t="s">
         <v>692</v>
       </c>
-      <c r="B232" t="s">
+      <c r="C232" t="s">
         <v>693</v>
-      </c>
-      <c r="C232" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B233" t="s">
         <v>695</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>696</v>
-      </c>
-      <c r="C233" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B234" t="s">
         <v>698</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C234" t="s">
         <v>699</v>
-      </c>
-      <c r="C234" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B235" t="s">
         <v>701</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>702</v>
-      </c>
-      <c r="C235" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B236" t="s">
         <v>704</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" t="s">
         <v>705</v>
-      </c>
-      <c r="C236" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B237" t="s">
         <v>707</v>
       </c>
-      <c r="B237" t="s">
+      <c r="C237" t="s">
         <v>708</v>
-      </c>
-      <c r="C237" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B238" t="s">
         <v>710</v>
       </c>
-      <c r="B238" t="s">
+      <c r="C238" t="s">
         <v>711</v>
-      </c>
-      <c r="C238" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B239" t="s">
         <v>713</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" t="s">
         <v>714</v>
-      </c>
-      <c r="C239" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B240" t="s">
         <v>716</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>717</v>
-      </c>
-      <c r="C240" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B241" t="s">
         <v>719</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C241" t="s">
         <v>720</v>
-      </c>
-      <c r="C241" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B242" t="s">
         <v>722</v>
       </c>
-      <c r="B242" t="s">
+      <c r="C242" t="s">
         <v>723</v>
-      </c>
-      <c r="C242" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B243" t="s">
         <v>725</v>
       </c>
-      <c r="B243" t="s">
+      <c r="C243" t="s">
         <v>726</v>
-      </c>
-      <c r="C243" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B244" t="s">
         <v>728</v>
       </c>
-      <c r="B244" t="s">
+      <c r="C244" t="s">
         <v>729</v>
-      </c>
-      <c r="C244" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B245" t="s">
         <v>731</v>
       </c>
-      <c r="B245" t="s">
+      <c r="C245" t="s">
         <v>732</v>
-      </c>
-      <c r="C245" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B246" t="s">
         <v>734</v>
       </c>
-      <c r="B246" t="s">
+      <c r="C246" t="s">
         <v>735</v>
-      </c>
-      <c r="C246" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B247" t="s">
         <v>737</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" t="s">
         <v>738</v>
-      </c>
-      <c r="C247" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B248" t="s">
         <v>740</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>741</v>
-      </c>
-      <c r="C248" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="249" spans="1:3">
       <c r="A249" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B249" t="s">
         <v>743</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>744</v>
-      </c>
-      <c r="C249" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="250" spans="1:3">
       <c r="A250" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B250" t="s">
         <v>746</v>
       </c>
-      <c r="B250" t="s">
+      <c r="C250" t="s">
         <v>747</v>
-      </c>
-      <c r="C250" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="251" spans="1:3">
       <c r="A251" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B251" t="s">
         <v>749</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C251" t="s">
         <v>750</v>
-      </c>
-      <c r="C251" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B252" t="s">
         <v>752</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C252" t="s">
         <v>753</v>
-      </c>
-      <c r="C252" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B253" t="s">
         <v>755</v>
       </c>
-      <c r="B253" t="s">
+      <c r="C253" t="s">
         <v>756</v>
-      </c>
-      <c r="C253" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="254" spans="1:3">
       <c r="A254" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B254" t="s">
         <v>758</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C254" t="s">
         <v>759</v>
-      </c>
-      <c r="C254" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B255" t="s">
         <v>761</v>
       </c>
-      <c r="B255" t="s">
+      <c r="C255" t="s">
         <v>762</v>
-      </c>
-      <c r="C255" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B256" t="s">
         <v>764</v>
       </c>
-      <c r="B256" t="s">
+      <c r="C256" t="s">
         <v>765</v>
-      </c>
-      <c r="C256" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B257" t="s">
         <v>767</v>
       </c>
-      <c r="B257" t="s">
+      <c r="C257" t="s">
         <v>768</v>
-      </c>
-      <c r="C257" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B258" t="s">
         <v>770</v>
       </c>
-      <c r="B258" t="s">
+      <c r="C258" t="s">
         <v>771</v>
-      </c>
-      <c r="C258" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B259" t="s">
         <v>773</v>
       </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
         <v>774</v>
-      </c>
-      <c r="C259" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B260" t="s">
         <v>776</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" t="s">
         <v>777</v>
-      </c>
-      <c r="C260" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B261" t="s">
         <v>779</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" t="s">
         <v>780</v>
-      </c>
-      <c r="C261" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="262" spans="1:3">
       <c r="A262" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B262" t="s">
         <v>782</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" t="s">
         <v>783</v>
-      </c>
-      <c r="C262" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -7501,1503 +7524,1541 @@
         <v>788</v>
       </c>
       <c r="C264" t="s">
-        <v>789</v>
+        <v>729</v>
       </c>
     </row>
     <row r="265" spans="1:3">
       <c r="A265" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B265" t="s">
         <v>790</v>
       </c>
-      <c r="B265" t="s">
+      <c r="C265" t="s">
         <v>791</v>
-      </c>
-      <c r="C265" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B266" t="s">
         <v>793</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" t="s">
         <v>794</v>
-      </c>
-      <c r="C266" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B267" t="s">
         <v>796</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C267" t="s">
         <v>797</v>
-      </c>
-      <c r="C267" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B268" t="s">
         <v>799</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" t="s">
         <v>800</v>
-      </c>
-      <c r="C268" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B269" t="s">
         <v>802</v>
       </c>
-      <c r="B269" t="s">
+      <c r="C269" t="s">
         <v>803</v>
-      </c>
-      <c r="C269" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B270" t="s">
         <v>805</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C270" t="s">
         <v>806</v>
-      </c>
-      <c r="C270" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B271" t="s">
         <v>808</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C271" t="s">
         <v>809</v>
-      </c>
-      <c r="C271" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B272" t="s">
         <v>811</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>812</v>
-      </c>
-      <c r="C272" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B273" t="s">
         <v>814</v>
       </c>
-      <c r="B273" t="s">
+      <c r="C273" t="s">
         <v>815</v>
-      </c>
-      <c r="C273" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B274" t="s">
         <v>817</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C274" t="s">
         <v>818</v>
-      </c>
-      <c r="C274" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B275" t="s">
         <v>820</v>
       </c>
-      <c r="B275" t="s">
+      <c r="C275" t="s">
         <v>821</v>
-      </c>
-      <c r="C275" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B276" t="s">
         <v>823</v>
       </c>
-      <c r="B276" t="s">
+      <c r="C276" t="s">
         <v>824</v>
-      </c>
-      <c r="C276" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B277" t="s">
         <v>826</v>
       </c>
-      <c r="B277" t="s">
+      <c r="C277" t="s">
         <v>827</v>
-      </c>
-      <c r="C277" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="278" spans="1:3">
       <c r="A278" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B278" t="s">
         <v>829</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>830</v>
-      </c>
-      <c r="C278" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B279" t="s">
         <v>832</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C279" t="s">
         <v>833</v>
-      </c>
-      <c r="C279" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="280" spans="1:3">
       <c r="A280" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B280" t="s">
         <v>835</v>
       </c>
-      <c r="B280" t="s">
+      <c r="C280" t="s">
         <v>836</v>
-      </c>
-      <c r="C280" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="281" spans="1:3">
       <c r="A281" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B281" t="s">
         <v>838</v>
       </c>
-      <c r="B281" t="s">
+      <c r="C281" t="s">
         <v>839</v>
-      </c>
-      <c r="C281" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B282" t="s">
         <v>841</v>
       </c>
-      <c r="B282" t="s">
+      <c r="C282" t="s">
         <v>842</v>
-      </c>
-      <c r="C282" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="283" spans="1:3">
       <c r="A283" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B283" t="s">
         <v>844</v>
       </c>
-      <c r="B283" t="s">
+      <c r="C283" t="s">
         <v>845</v>
-      </c>
-      <c r="C283" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B284" t="s">
         <v>847</v>
       </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
         <v>848</v>
-      </c>
-      <c r="C284" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B285" t="s">
         <v>850</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C285" t="s">
         <v>851</v>
-      </c>
-      <c r="C285" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B286" t="s">
         <v>853</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C286" t="s">
         <v>854</v>
-      </c>
-      <c r="C286" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B287" t="s">
         <v>856</v>
       </c>
-      <c r="B287" t="s">
+      <c r="C287" t="s">
         <v>857</v>
-      </c>
-      <c r="C287" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B288" t="s">
         <v>859</v>
       </c>
-      <c r="B288" t="s">
+      <c r="C288" t="s">
         <v>860</v>
-      </c>
-      <c r="C288" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B289" t="s">
         <v>862</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C289" t="s">
         <v>863</v>
-      </c>
-      <c r="C289" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B290" t="s">
         <v>865</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C290" t="s">
         <v>866</v>
-      </c>
-      <c r="C290" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B291" t="s">
         <v>868</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C291" t="s">
         <v>869</v>
-      </c>
-      <c r="C291" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B292" t="s">
         <v>871</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C292" t="s">
         <v>872</v>
-      </c>
-      <c r="C292" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B293" t="s">
         <v>874</v>
       </c>
-      <c r="B293" t="s">
+      <c r="C293" t="s">
         <v>875</v>
-      </c>
-      <c r="C293" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B294" t="s">
         <v>877</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C294" t="s">
         <v>878</v>
-      </c>
-      <c r="C294" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B295" t="s">
         <v>880</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" t="s">
         <v>881</v>
-      </c>
-      <c r="C295" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B296" t="s">
         <v>883</v>
       </c>
-      <c r="B296" t="s">
+      <c r="C296" t="s">
         <v>884</v>
-      </c>
-      <c r="C296" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B297" t="s">
         <v>886</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" t="s">
         <v>887</v>
-      </c>
-      <c r="C297" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B298" t="s">
         <v>889</v>
       </c>
-      <c r="B298" t="s">
+      <c r="C298" t="s">
         <v>890</v>
-      </c>
-      <c r="C298" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B299" t="s">
         <v>892</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C299" t="s">
         <v>893</v>
-      </c>
-      <c r="C299" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B300" t="s">
         <v>895</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C300" t="s">
         <v>896</v>
-      </c>
-      <c r="C300" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B301" t="s">
         <v>898</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" t="s">
         <v>899</v>
-      </c>
-      <c r="C301" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B302" t="s">
         <v>901</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>902</v>
-      </c>
-      <c r="C302" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="303" spans="1:3">
       <c r="A303" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B303" t="s">
         <v>904</v>
       </c>
-      <c r="B303" t="s">
+      <c r="C303" t="s">
         <v>905</v>
-      </c>
-      <c r="C303" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="304" spans="1:3">
       <c r="A304" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B304" t="s">
         <v>907</v>
       </c>
-      <c r="B304" t="s">
+      <c r="C304" t="s">
         <v>908</v>
-      </c>
-      <c r="C304" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="305" spans="1:3">
       <c r="A305" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B305" t="s">
         <v>910</v>
       </c>
-      <c r="B305" t="s">
+      <c r="C305" t="s">
         <v>911</v>
-      </c>
-      <c r="C305" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B306" t="s">
         <v>913</v>
       </c>
-      <c r="B306" t="s">
+      <c r="C306" t="s">
         <v>914</v>
-      </c>
-      <c r="C306" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="307" spans="1:3">
       <c r="A307" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B307" t="s">
         <v>916</v>
       </c>
-      <c r="B307" t="s">
+      <c r="C307" t="s">
         <v>917</v>
-      </c>
-      <c r="C307" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="308" spans="1:3">
       <c r="A308" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B308" t="s">
         <v>919</v>
       </c>
-      <c r="B308" t="s">
+      <c r="C308" t="s">
         <v>920</v>
-      </c>
-      <c r="C308" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="309" spans="1:3">
       <c r="A309" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B309" t="s">
         <v>922</v>
       </c>
-      <c r="B309" t="s">
+      <c r="C309" t="s">
         <v>923</v>
-      </c>
-      <c r="C309" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B310" t="s">
         <v>925</v>
       </c>
-      <c r="B310" t="s">
+      <c r="C310" t="s">
         <v>926</v>
-      </c>
-      <c r="C310" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B311" t="s">
         <v>928</v>
       </c>
-      <c r="B311" t="s">
+      <c r="C311" t="s">
         <v>929</v>
-      </c>
-      <c r="C311" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B312" t="s">
         <v>931</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C312" t="s">
         <v>932</v>
-      </c>
-      <c r="C312" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B313" t="s">
         <v>934</v>
       </c>
-      <c r="B313" t="s">
+      <c r="C313" t="s">
         <v>935</v>
-      </c>
-      <c r="C313" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="314" spans="1:3">
       <c r="A314" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B314" t="s">
         <v>937</v>
       </c>
-      <c r="B314" t="s">
+      <c r="C314" t="s">
         <v>938</v>
-      </c>
-      <c r="C314" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B315" t="s">
         <v>940</v>
       </c>
-      <c r="B315" t="s">
+      <c r="C315" t="s">
         <v>941</v>
-      </c>
-      <c r="C315" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B316" t="s">
         <v>943</v>
       </c>
-      <c r="B316" t="s">
+      <c r="C316" t="s">
         <v>944</v>
-      </c>
-      <c r="C316" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B317" t="s">
         <v>946</v>
       </c>
-      <c r="B317" t="s">
+      <c r="C317" t="s">
         <v>947</v>
-      </c>
-      <c r="C317" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="318" spans="1:3">
       <c r="A318" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="B318" t="s">
         <v>949</v>
       </c>
-      <c r="B318" t="s">
+      <c r="C318" t="s">
         <v>950</v>
-      </c>
-      <c r="C318" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="B319" t="s">
         <v>952</v>
       </c>
-      <c r="B319" t="s">
+      <c r="C319" t="s">
         <v>953</v>
-      </c>
-      <c r="C319" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="320" spans="1:3">
       <c r="A320" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B320" t="s">
         <v>955</v>
       </c>
-      <c r="B320" t="s">
+      <c r="C320" t="s">
         <v>956</v>
-      </c>
-      <c r="C320" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="321" spans="1:3">
       <c r="A321" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B321" t="s">
         <v>958</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C321" t="s">
         <v>959</v>
-      </c>
-      <c r="C321" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="322" spans="1:3">
       <c r="A322" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B322" t="s">
         <v>961</v>
       </c>
-      <c r="B322" t="s">
+      <c r="C322" t="s">
         <v>962</v>
       </c>
-      <c r="C322" t="s">
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="1" t="s">
         <v>963</v>
       </c>
-    </row>
-    <row r="323" spans="1:3">
-      <c r="A323" s="1" t="s">
+      <c r="B323" t="s">
         <v>964</v>
-      </c>
-      <c r="B323" t="s">
-        <v>965</v>
-      </c>
-      <c r="C323" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B324" t="s">
+        <v>966</v>
+      </c>
+      <c r="C324" t="s">
         <v>967</v>
-      </c>
-      <c r="B324" t="s">
-        <v>968</v>
-      </c>
-      <c r="C324" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="325" spans="1:3">
       <c r="A325" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B325" t="s">
+        <v>969</v>
+      </c>
+      <c r="C325" t="s">
         <v>970</v>
-      </c>
-      <c r="B325" t="s">
-        <v>971</v>
-      </c>
-      <c r="C325" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B326" t="s">
+        <v>972</v>
+      </c>
+      <c r="C326" t="s">
         <v>973</v>
-      </c>
-      <c r="B326" t="s">
-        <v>974</v>
-      </c>
-      <c r="C326" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="327" spans="1:3">
       <c r="A327" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B327" t="s">
+        <v>975</v>
+      </c>
+      <c r="C327" t="s">
         <v>976</v>
-      </c>
-      <c r="B327" t="s">
-        <v>977</v>
-      </c>
-      <c r="C327" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B328" t="s">
+        <v>978</v>
+      </c>
+      <c r="C328" t="s">
         <v>979</v>
-      </c>
-      <c r="B328" t="s">
-        <v>980</v>
-      </c>
-      <c r="C328" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B329" t="s">
+        <v>981</v>
+      </c>
+      <c r="C329" t="s">
         <v>982</v>
-      </c>
-      <c r="B329" t="s">
-        <v>983</v>
-      </c>
-      <c r="C329" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B330" t="s">
+        <v>984</v>
+      </c>
+      <c r="C330" t="s">
         <v>985</v>
-      </c>
-      <c r="B330" t="s">
-        <v>986</v>
-      </c>
-      <c r="C330" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B331" t="s">
+        <v>987</v>
+      </c>
+      <c r="C331" t="s">
         <v>988</v>
-      </c>
-      <c r="B331" t="s">
-        <v>989</v>
-      </c>
-      <c r="C331" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="332" spans="1:3">
       <c r="A332" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B332" t="s">
         <v>990</v>
       </c>
-      <c r="B332" t="s">
+      <c r="C332" t="s">
         <v>991</v>
-      </c>
-      <c r="C332" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="333" spans="1:3">
       <c r="A333" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B333" t="s">
         <v>993</v>
       </c>
-      <c r="B333" t="s">
+      <c r="C333" t="s">
         <v>994</v>
-      </c>
-      <c r="C333" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="334" spans="1:3">
       <c r="A334" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B334" t="s">
         <v>996</v>
       </c>
-      <c r="B334" t="s">
-        <v>997</v>
-      </c>
       <c r="C334" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
     </row>
     <row r="335" spans="1:3">
       <c r="A335" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B335" t="s">
+        <v>998</v>
+      </c>
+      <c r="C335" t="s">
         <v>999</v>
-      </c>
-      <c r="B335" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C335" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C336" t="s">
         <v>1002</v>
-      </c>
-      <c r="B336" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C336" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C337" t="s">
         <v>1005</v>
-      </c>
-      <c r="B337" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C337" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C338" t="s">
         <v>1008</v>
-      </c>
-      <c r="B338" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="339" spans="1:3">
       <c r="A339" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C339" t="s">
         <v>1011</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C339" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="340" spans="1:3">
       <c r="A340" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C340" t="s">
         <v>1014</v>
-      </c>
-      <c r="B340" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C340" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="341" spans="1:3">
       <c r="A341" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C341" t="s">
         <v>1017</v>
-      </c>
-      <c r="B341" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C341" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C342" t="s">
         <v>1020</v>
-      </c>
-      <c r="B342" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C342" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C343" t="s">
         <v>1023</v>
-      </c>
-      <c r="B343" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C343" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C344" t="s">
         <v>1026</v>
-      </c>
-      <c r="B344" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C344" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C345" t="s">
         <v>1029</v>
-      </c>
-      <c r="B345" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C345" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C346" t="s">
         <v>1032</v>
-      </c>
-      <c r="B346" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C346" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C347" t="s">
         <v>1035</v>
-      </c>
-      <c r="B347" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C348" t="s">
         <v>1038</v>
-      </c>
-      <c r="B348" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C349" t="s">
         <v>1041</v>
-      </c>
-      <c r="B349" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C350" t="s">
         <v>1044</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C351" t="s">
         <v>1047</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C352" t="s">
         <v>1050</v>
-      </c>
-      <c r="B352" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C352" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C353" t="s">
         <v>1053</v>
-      </c>
-      <c r="B353" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C353" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C354" t="s">
         <v>1056</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C354" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C355" t="s">
         <v>1059</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C355" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C356" t="s">
         <v>1062</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C356" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C357" t="s">
         <v>1065</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C357" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C358" t="s">
         <v>1068</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C358" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C359" t="s">
         <v>1071</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C359" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C360" t="s">
         <v>1074</v>
-      </c>
-      <c r="B360" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C360" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C361" t="s">
         <v>1077</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C361" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C362" t="s">
         <v>1080</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C362" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C363" t="s">
         <v>1083</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C363" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C364" t="s">
         <v>1086</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="365" spans="1:3">
       <c r="A365" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C365" t="s">
         <v>1089</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="366" spans="1:3">
       <c r="A366" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C366" t="s">
         <v>1092</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="367" spans="1:3">
       <c r="A367" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C367" t="s">
         <v>1095</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C368" t="s">
         <v>1098</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="369" spans="1:3">
       <c r="A369" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C369" t="s">
         <v>1101</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="370" spans="1:3">
       <c r="A370" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C370" t="s">
         <v>1104</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="371" spans="1:3">
       <c r="A371" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C371" t="s">
         <v>1107</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="372" spans="1:3">
       <c r="A372" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C372" t="s">
         <v>1110</v>
-      </c>
-      <c r="B372" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C372" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="373" spans="1:3">
       <c r="A373" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C373" t="s">
         <v>1113</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C374" t="s">
         <v>1116</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="375" spans="1:3">
       <c r="A375" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C375" t="s">
         <v>1119</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C376" t="s">
         <v>1122</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="377" spans="1:3">
       <c r="A377" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C377" t="s">
         <v>1125</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C377" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="378" spans="1:3">
       <c r="A378" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C378" t="s">
         <v>1128</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C379" t="s">
         <v>1131</v>
-      </c>
-      <c r="B379" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B380" t="s">
         <v>1133</v>
       </c>
-      <c r="B380" t="s">
+      <c r="C380" t="s">
         <v>1134</v>
-      </c>
-      <c r="C380" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B381" t="s">
         <v>1136</v>
       </c>
-      <c r="B381" t="s">
+      <c r="C381" t="s">
         <v>1137</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B382" t="s">
         <v>1139</v>
       </c>
-      <c r="B382" t="s">
-        <v>1140</v>
-      </c>
       <c r="C382" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C383" t="s">
         <v>1142</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C383" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C384" t="s">
         <v>1145</v>
-      </c>
-      <c r="B384" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C384" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="385" spans="1:3">
       <c r="A385" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C385" t="s">
         <v>1148</v>
-      </c>
-      <c r="B385" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C385" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="386" spans="1:3">
       <c r="A386" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C386" t="s">
         <v>1151</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="387" spans="1:3">
       <c r="A387" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C387" t="s">
         <v>1154</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="388" spans="1:3">
       <c r="A388" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C388" t="s">
         <v>1157</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C388" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="389" spans="1:3">
       <c r="A389" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C389" t="s">
         <v>1160</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="390" spans="1:3">
       <c r="A390" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C390" t="s">
         <v>1163</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="391" spans="1:3">
       <c r="A391" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C391" t="s">
         <v>1166</v>
-      </c>
-      <c r="B391" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="392" spans="1:3">
       <c r="A392" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C392" t="s">
         <v>1169</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="393" spans="1:3">
       <c r="A393" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B393" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C393" t="s">
         <v>1172</v>
-      </c>
-      <c r="B393" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C393" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="394" spans="1:3">
       <c r="A394" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C394" t="s">
         <v>1175</v>
-      </c>
-      <c r="B394" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C394" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="395" spans="1:3">
       <c r="A395" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C395" t="s">
         <v>1178</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="396" spans="1:3">
       <c r="A396" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C396" t="s">
         <v>1181</v>
-      </c>
-      <c r="B396" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C396" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="397" spans="1:3">
       <c r="A397" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C397" t="s">
         <v>1184</v>
-      </c>
-      <c r="B397" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C397" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="398" spans="1:3">
       <c r="A398" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C398" t="s">
         <v>1187</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C398" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C399" t="s">
         <v>1190</v>
-      </c>
-      <c r="B399" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C399" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="400" spans="1:3">
       <c r="A400" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C400" t="s">
         <v>1193</v>
       </c>
-      <c r="B400" t="s">
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="C400" t="s">
-        <v>1124</v>
+      <c r="B401" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C401" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C403" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>1203</v>
       </c>
     </row>
   </sheetData>
